--- a/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
+++ b/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
@@ -71,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,12 +85,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -100,12 +100,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,23 +148,14 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -177,29 +163,29 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,14 +673,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -731,11 +717,11 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Пример подстановки. Система 1, выход 1-го РИС-н (X, Y, Z с экрана):</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>Реактор 1, вход (τ = 0; с экрана):</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Величина</t>
@@ -748,7 +734,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>X, Y, Z с экрана</t>
+          <t>С экрана</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -758,7 +744,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>CA, CR, CS, моль/л</t>
+          <t>Результат, моль/л</t>
         </is>
       </c>
     </row>
@@ -775,16 +761,16 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>X = 0.2308</t>
+          <t>X = 0,0000</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>30·(1−0.2308)</t>
+          <t>30·(1−0,0000)</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>23.076</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -800,16 +786,16 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Y = 0.1923</t>
+          <t>Y = 0,0000</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>30·0.1923</t>
+          <t>30·0,0000</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -825,311 +811,1467 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Z = 0.0385</t>
+          <t>Z = 0,0000</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>30·0.0385</t>
+          <t>30·0,0000</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Реактор 1, выход (τ = 0,5; с экрана):</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,2308</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,2308)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>23.076</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,1923</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>30·0,1923</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>5.769</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,0385</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>30·0,0385</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
         <v>1.155</v>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Реальные концентрации на выходе каждого реактора (те же формулы, X Y Z с экрана / модели):</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Схема / аппарат</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Реактор 2, вход (τ = 0; с экрана):</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,2308</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,2308)</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>23.076</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,1923</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>30·0,1923</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>5.769</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Вход в систему</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>1. 4 РИС-н в ряду, реактор 1</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>0.1923</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>23.076</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>5.769</v>
-      </c>
-      <c r="H18" s="6" t="n">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,0385</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>30·0,0385</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
         <v>1.155</v>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>1. 4 РИС-н в ряду, реактор 2</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>0.4083</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>0.3082</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>0.1001</v>
-      </c>
-      <c r="F19" s="6" t="n">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Реактор 2, выход (τ = 0,5; с экрана):</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,4083</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,4083)</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
         <v>17.751</v>
       </c>
-      <c r="G19" s="6" t="n">
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,3082</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>30·0,3082</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
         <v>9.245999999999999</v>
       </c>
-      <c r="H19" s="6" t="n">
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,1001</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>30·0,1001</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
         <v>3.003</v>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>1. 4 РИС-н в ряду, реактор 3</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>0.5448</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>0.3706</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>0.1742</v>
-      </c>
-      <c r="F20" s="6" t="n">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Реактор 3, вход (τ = 0; с экрана):</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,4083</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,4083)</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>17.751</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,3082</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>30·0,3082</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>9.245999999999999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,1001</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>30·0,1001</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>3.003</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Реактор 3, выход (τ = 0,5; с экрана):</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,5448</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,5448)</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
         <v>13.656</v>
       </c>
-      <c r="G20" s="6" t="n">
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,3706</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>30·0,3706</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n">
         <v>11.118</v>
       </c>
-      <c r="H20" s="6" t="n">
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,1742</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>30·0,1742</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
         <v>5.226</v>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>1. 4 РИС-н в ряду, реактор 4 (выход системы)</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>0.6498</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>0.3964</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>0.2535</v>
-      </c>
-      <c r="F21" s="13" t="n">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Реактор 4, вход (τ = 0; с экрана):</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,5448</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,5448)</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>13.656</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,3706</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>30·0,3706</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>11.118</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,1742</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>30·0,1742</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>5.226</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Реактор 4, выход (τ = 0,5; выход системы 1, с экрана):</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,6498</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,6498)</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
         <v>10.506</v>
       </c>
-      <c r="G21" s="13" t="n">
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,3964</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>30·0,3964</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
         <v>11.892</v>
       </c>
-      <c r="H21" s="13" t="n">
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,2535</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>30·0,2535</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
         <v>7.605</v>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>2. 4 РИС-н параллельно, каждый / выход</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>0.5454</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>0.2424</v>
-      </c>
-      <c r="F22" s="6" t="n">
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Система 2, каждый из 4 параллельных РИС-н / выход (τi = 2 мин):</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,5454</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,5454)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
         <v>13.638</v>
       </c>
-      <c r="G22" s="6" t="n">
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,3030</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>30·0,3030</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
         <v>9.09</v>
       </c>
-      <c r="H22" s="6" t="n">
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,2424</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>30·0,2424</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
         <v>7.272</v>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>3. 4 РИВ в ряду, выход системы</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="F23" s="16" t="n">
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Система 3, выход 1-го РИВ (τi = 0,5 мин):</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,2592</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,2592)</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>22.224</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,2337</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>30·0,2337</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>7.011</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,0254</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>30·0,0254</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>0.762</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Система 3, выход 2-го РИВ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,4512</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,4512)</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>16.464</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,3645</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>30·0,3645</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>10.935</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,0867</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>30·0,0867</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>2.601</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Система 3, выход 3-го РИВ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,5934</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,5934)</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>12.198</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,4267</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>30·0,4267</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>12.801</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,1667</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>30·0,1667</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>5.000999999999999</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Система 3, выход 4-го РИВ — выход системы:</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,6988</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,6988)</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="G23" s="16" t="n">
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,4444</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>30·0,4444</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n">
         <v>13.332</v>
       </c>
-      <c r="H23" s="16" t="n">
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,2544</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>30·0,2544</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="n">
         <v>7.632000000000001</v>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>4. 4 РИВ параллельно, каждый / выход</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="F24" s="16" t="n">
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Система 4, каждый из 4 параллельных РИВ / выход (τi = 2 мин):</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="24" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Величина</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Формула</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>С экрана</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Подстановка</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Результат, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>CA0·(1−X)</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>X = 0,6988</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>30·(1−0,6988)</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="G24" s="16" t="n">
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Y</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Y = 0,4444</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>30·0,4444</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="n">
         <v>13.332</v>
       </c>
-      <c r="H24" s="16" t="n">
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>CA0·Z</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Z = 0,2544</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>30·0,2544</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="n">
         <v>7.632000000000001</v>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Проверка материального баланса: CA + CR + CS = CA0, то есть (1−X) + Y + Z = 1. Для выхода 1-го РИС-н: (1−0,2308)+0,1923+0,0385 = 1,0000. Для выхода системы 1: (1−0,6498)+0,3964+0,2535 = 1,0001 (округление экрана). Дальше все таблицы пункта 2 считаются этими же формулами.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1"/>
-    <row r="28" ht="20" customHeight="1"/>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Проверка: CA + CR + CS = CA0, то есть (1−X) + Y + Z = 1. Расхождения в 0,01 моль/л — округление X, Y, Z на экране. Дальше все таблицы пункта 2 считаются этими же формулами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108"/>
+    <row r="109"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A26:H28"/>
+  <mergeCells count="18">
+    <mergeCell ref="A93:G93"/>
     <mergeCell ref="A4:H7"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A58:G58"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A79:G79"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A100:G100"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A107:H109"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1159,14 +2301,14 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Система 1. Четыре последовательно соединённых РИС-н одинакового объёма  (vi = 50 л/мин, τi = 0,5 мин). Экран программы.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Реактор 1</t>
         </is>
@@ -1213,19 +2355,19 @@
       <c r="A7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
@@ -1233,30 +2375,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="11" t="n">
         <v>0.2308</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="10" t="n">
         <v>23.076</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="11" t="n">
         <v>0.1923</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="10" t="n">
         <v>5.769</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="11" t="n">
         <v>0.0385</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="10" t="n">
         <v>1.155</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Реактор 2</t>
         </is>
@@ -1303,19 +2445,19 @@
       <c r="A13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="9" t="n">
         <v>0.2308</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>23.076</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="9" t="n">
         <v>0.1923</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>5.769</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="9" t="n">
         <v>0.0385</v>
       </c>
       <c r="G13" s="6" t="n">
@@ -1323,30 +2465,30 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="11" t="n">
         <v>0.4083</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="10" t="n">
         <v>17.751</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="11" t="n">
         <v>0.3082</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="10" t="n">
         <v>9.245999999999999</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="11" t="n">
         <v>0.1001</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="10" t="n">
         <v>3.003</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Реактор 3</t>
         </is>
@@ -1393,19 +2535,19 @@
       <c r="A19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="9" t="n">
         <v>0.4083</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>17.751</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="9" t="n">
         <v>0.3082</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>9.245999999999999</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="9" t="n">
         <v>0.1001</v>
       </c>
       <c r="G19" s="6" t="n">
@@ -1413,30 +2555,30 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="11" t="n">
         <v>0.5448</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="10" t="n">
         <v>13.656</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="11" t="n">
         <v>0.3706</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E20" s="10" t="n">
         <v>11.118</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="11" t="n">
         <v>0.1742</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="10" t="n">
         <v>5.226</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Реактор 4</t>
         </is>
@@ -1483,19 +2625,19 @@
       <c r="A25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="9" t="n">
         <v>0.5448</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>13.656</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="9" t="n">
         <v>0.3706</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>11.118</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="9" t="n">
         <v>0.1742</v>
       </c>
       <c r="G25" s="6" t="n">
@@ -1503,37 +2645,37 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="11" t="n">
         <v>0.6498</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="10" t="n">
         <v>10.506</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="11" t="n">
         <v>0.3964</v>
       </c>
-      <c r="E26" s="20" t="n">
+      <c r="E26" s="10" t="n">
         <v>11.892</v>
       </c>
-      <c r="F26" s="21" t="n">
+      <c r="F26" s="11" t="n">
         <v>0.2535</v>
       </c>
-      <c r="G26" s="20" t="n">
+      <c r="G26" s="10" t="n">
         <v>7.605</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Система 2. Четыре параллельно соединённых РИС-н одинакового объёма, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Реактор 1</t>
         </is>
@@ -1580,19 +2722,19 @@
       <c r="A33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
@@ -1600,30 +2742,30 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="n">
+      <c r="A34" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="21" t="n">
+      <c r="B34" s="11" t="n">
         <v>0.5454</v>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="10" t="n">
         <v>13.638</v>
       </c>
-      <c r="D34" s="21" t="n">
+      <c r="D34" s="11" t="n">
         <v>0.303</v>
       </c>
-      <c r="E34" s="20" t="n">
+      <c r="E34" s="10" t="n">
         <v>9.09</v>
       </c>
-      <c r="F34" s="21" t="n">
+      <c r="F34" s="11" t="n">
         <v>0.2424</v>
       </c>
-      <c r="G34" s="20" t="n">
+      <c r="G34" s="10" t="n">
         <v>7.272</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Реактор 2</t>
         </is>
@@ -1670,19 +2812,19 @@
       <c r="A39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
@@ -1690,30 +2832,30 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="n">
+      <c r="A40" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="21" t="n">
+      <c r="B40" s="11" t="n">
         <v>0.5454</v>
       </c>
-      <c r="C40" s="20" t="n">
+      <c r="C40" s="10" t="n">
         <v>13.638</v>
       </c>
-      <c r="D40" s="21" t="n">
+      <c r="D40" s="11" t="n">
         <v>0.303</v>
       </c>
-      <c r="E40" s="20" t="n">
+      <c r="E40" s="10" t="n">
         <v>9.09</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="F40" s="11" t="n">
         <v>0.2424</v>
       </c>
-      <c r="G40" s="20" t="n">
+      <c r="G40" s="10" t="n">
         <v>7.272</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Реактор 3</t>
         </is>
@@ -1760,19 +2902,19 @@
       <c r="A45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="11" t="n">
+      <c r="F45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
@@ -1780,30 +2922,30 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="n">
+      <c r="A46" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="21" t="n">
+      <c r="B46" s="11" t="n">
         <v>0.5454</v>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="10" t="n">
         <v>13.638</v>
       </c>
-      <c r="D46" s="21" t="n">
+      <c r="D46" s="11" t="n">
         <v>0.303</v>
       </c>
-      <c r="E46" s="20" t="n">
+      <c r="E46" s="10" t="n">
         <v>9.09</v>
       </c>
-      <c r="F46" s="21" t="n">
+      <c r="F46" s="11" t="n">
         <v>0.2424</v>
       </c>
-      <c r="G46" s="20" t="n">
+      <c r="G46" s="10" t="n">
         <v>7.272</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Реактор 4</t>
         </is>
@@ -1850,19 +2992,19 @@
       <c r="A51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B51" s="11" t="n">
+      <c r="B51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="11" t="n">
+      <c r="F51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
@@ -1870,37 +3012,37 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="n">
+      <c r="A52" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B52" s="21" t="n">
+      <c r="B52" s="11" t="n">
         <v>0.5454</v>
       </c>
-      <c r="C52" s="20" t="n">
+      <c r="C52" s="10" t="n">
         <v>13.638</v>
       </c>
-      <c r="D52" s="21" t="n">
+      <c r="D52" s="11" t="n">
         <v>0.303</v>
       </c>
-      <c r="E52" s="20" t="n">
+      <c r="E52" s="10" t="n">
         <v>9.09</v>
       </c>
-      <c r="F52" s="21" t="n">
+      <c r="F52" s="11" t="n">
         <v>0.2424</v>
       </c>
-      <c r="G52" s="20" t="n">
+      <c r="G52" s="10" t="n">
         <v>7.272</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>Система 3. Четыре последовательно соединённых РИВ одинакового объёма (vi = 50 л/мин, τi = 0,5 мин).</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="19" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>Реактор 1</t>
         </is>
@@ -1947,19 +3089,19 @@
       <c r="A59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B59" s="11" t="n">
+      <c r="B59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D59" s="11" t="n">
+      <c r="D59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F59" s="11" t="n">
+      <c r="F59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="6" t="n">
@@ -1967,25 +3109,25 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="20" t="n">
+      <c r="A60" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="B60" s="21" t="n">
+      <c r="B60" s="11" t="n">
         <v>0.0582</v>
       </c>
-      <c r="C60" s="20" t="n">
+      <c r="C60" s="10" t="n">
         <v>28.254</v>
       </c>
-      <c r="D60" s="21" t="n">
+      <c r="D60" s="11" t="n">
         <v>0.0571</v>
       </c>
-      <c r="E60" s="20" t="n">
+      <c r="E60" s="10" t="n">
         <v>1.713</v>
       </c>
-      <c r="F60" s="21" t="n">
+      <c r="F60" s="11" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G60" s="20" t="n">
+      <c r="G60" s="10" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -1993,19 +3135,19 @@
       <c r="A61" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="B61" s="11" t="n">
+      <c r="B61" s="9" t="n">
         <v>0.1131</v>
       </c>
       <c r="C61" s="6" t="n">
         <v>26.607</v>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D61" s="9" t="n">
         <v>0.1086</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>3.258</v>
       </c>
-      <c r="F61" s="11" t="n">
+      <c r="F61" s="9" t="n">
         <v>0.0045</v>
       </c>
       <c r="G61" s="6" t="n">
@@ -2013,25 +3155,25 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="20" t="n">
+      <c r="A62" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="B62" s="21" t="n">
+      <c r="B62" s="11" t="n">
         <v>0.1647</v>
       </c>
-      <c r="C62" s="20" t="n">
+      <c r="C62" s="10" t="n">
         <v>25.059</v>
       </c>
-      <c r="D62" s="21" t="n">
+      <c r="D62" s="11" t="n">
         <v>0.155</v>
       </c>
-      <c r="E62" s="20" t="n">
+      <c r="E62" s="10" t="n">
         <v>4.65</v>
       </c>
-      <c r="F62" s="21" t="n">
+      <c r="F62" s="11" t="n">
         <v>0.0098</v>
       </c>
-      <c r="G62" s="20" t="n">
+      <c r="G62" s="10" t="n">
         <v>0.294</v>
       </c>
     </row>
@@ -2039,19 +3181,19 @@
       <c r="A63" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="B63" s="11" t="n">
+      <c r="B63" s="9" t="n">
         <v>0.2134</v>
       </c>
       <c r="C63" s="6" t="n">
         <v>23.598</v>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D63" s="9" t="n">
         <v>0.1965</v>
       </c>
       <c r="E63" s="6" t="n">
         <v>5.895</v>
       </c>
-      <c r="F63" s="11" t="n">
+      <c r="F63" s="9" t="n">
         <v>0.0168</v>
       </c>
       <c r="G63" s="6" t="n">
@@ -2059,30 +3201,30 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="20" t="n">
+      <c r="A64" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B64" s="21" t="n">
+      <c r="B64" s="11" t="n">
         <v>0.2592</v>
       </c>
-      <c r="C64" s="20" t="n">
+      <c r="C64" s="10" t="n">
         <v>22.224</v>
       </c>
-      <c r="D64" s="21" t="n">
+      <c r="D64" s="11" t="n">
         <v>0.2337</v>
       </c>
-      <c r="E64" s="20" t="n">
+      <c r="E64" s="10" t="n">
         <v>7.011</v>
       </c>
-      <c r="F64" s="21" t="n">
+      <c r="F64" s="11" t="n">
         <v>0.0254</v>
       </c>
-      <c r="G64" s="20" t="n">
+      <c r="G64" s="10" t="n">
         <v>0.762</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Реактор 2</t>
         </is>
@@ -2129,19 +3271,19 @@
       <c r="A69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B69" s="11" t="n">
+      <c r="B69" s="9" t="n">
         <v>0.2592</v>
       </c>
       <c r="C69" s="6" t="n">
         <v>22.224</v>
       </c>
-      <c r="D69" s="11" t="n">
+      <c r="D69" s="9" t="n">
         <v>0.2337</v>
       </c>
       <c r="E69" s="6" t="n">
         <v>7.011</v>
       </c>
-      <c r="F69" s="11" t="n">
+      <c r="F69" s="9" t="n">
         <v>0.0254</v>
       </c>
       <c r="G69" s="6" t="n">
@@ -2149,25 +3291,25 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="20" t="n">
+      <c r="A70" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="B70" s="21" t="n">
+      <c r="B70" s="11" t="n">
         <v>0.3023</v>
       </c>
-      <c r="C70" s="20" t="n">
+      <c r="C70" s="10" t="n">
         <v>20.931</v>
       </c>
-      <c r="D70" s="21" t="n">
+      <c r="D70" s="11" t="n">
         <v>0.2669</v>
       </c>
-      <c r="E70" s="20" t="n">
+      <c r="E70" s="10" t="n">
         <v>8.007000000000001</v>
       </c>
-      <c r="F70" s="21" t="n">
+      <c r="F70" s="11" t="n">
         <v>0.0355</v>
       </c>
-      <c r="G70" s="20" t="n">
+      <c r="G70" s="10" t="n">
         <v>1.065</v>
       </c>
     </row>
@@ -2175,19 +3317,19 @@
       <c r="A71" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="B71" s="11" t="n">
+      <c r="B71" s="9" t="n">
         <v>0.343</v>
       </c>
       <c r="C71" s="6" t="n">
         <v>19.71</v>
       </c>
-      <c r="D71" s="11" t="n">
+      <c r="D71" s="9" t="n">
         <v>0.2962</v>
       </c>
       <c r="E71" s="6" t="n">
         <v>8.886000000000001</v>
       </c>
-      <c r="F71" s="11" t="n">
+      <c r="F71" s="9" t="n">
         <v>0.0467</v>
       </c>
       <c r="G71" s="6" t="n">
@@ -2195,25 +3337,25 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="20" t="n">
+      <c r="A72" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="B72" s="21" t="n">
+      <c r="B72" s="11" t="n">
         <v>0.3812</v>
       </c>
-      <c r="C72" s="20" t="n">
+      <c r="C72" s="10" t="n">
         <v>18.564</v>
       </c>
-      <c r="D72" s="21" t="n">
+      <c r="D72" s="11" t="n">
         <v>0.3221</v>
       </c>
-      <c r="E72" s="20" t="n">
+      <c r="E72" s="10" t="n">
         <v>9.663</v>
       </c>
-      <c r="F72" s="21" t="n">
+      <c r="F72" s="11" t="n">
         <v>0.0591</v>
       </c>
-      <c r="G72" s="20" t="n">
+      <c r="G72" s="10" t="n">
         <v>1.773</v>
       </c>
     </row>
@@ -2221,19 +3363,19 @@
       <c r="A73" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="B73" s="11" t="n">
+      <c r="B73" s="9" t="n">
         <v>0.4173</v>
       </c>
       <c r="C73" s="6" t="n">
         <v>17.481</v>
       </c>
-      <c r="D73" s="11" t="n">
+      <c r="D73" s="9" t="n">
         <v>0.3448</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>10.344</v>
       </c>
-      <c r="F73" s="11" t="n">
+      <c r="F73" s="9" t="n">
         <v>0.0725</v>
       </c>
       <c r="G73" s="6" t="n">
@@ -2241,30 +3383,30 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="20" t="n">
+      <c r="A74" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B74" s="21" t="n">
+      <c r="B74" s="11" t="n">
         <v>0.4512</v>
       </c>
-      <c r="C74" s="20" t="n">
+      <c r="C74" s="10" t="n">
         <v>16.464</v>
       </c>
-      <c r="D74" s="21" t="n">
+      <c r="D74" s="11" t="n">
         <v>0.3645</v>
       </c>
-      <c r="E74" s="20" t="n">
+      <c r="E74" s="10" t="n">
         <v>10.935</v>
       </c>
-      <c r="F74" s="21" t="n">
+      <c r="F74" s="11" t="n">
         <v>0.0867</v>
       </c>
-      <c r="G74" s="20" t="n">
+      <c r="G74" s="10" t="n">
         <v>2.601</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="19" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>Реактор 3</t>
         </is>
@@ -2311,19 +3453,19 @@
       <c r="A79" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B79" s="11" t="n">
+      <c r="B79" s="9" t="n">
         <v>0.4512</v>
       </c>
       <c r="C79" s="6" t="n">
         <v>16.464</v>
       </c>
-      <c r="D79" s="11" t="n">
+      <c r="D79" s="9" t="n">
         <v>0.3645</v>
       </c>
       <c r="E79" s="6" t="n">
         <v>10.935</v>
       </c>
-      <c r="F79" s="11" t="n">
+      <c r="F79" s="9" t="n">
         <v>0.0867</v>
       </c>
       <c r="G79" s="6" t="n">
@@ -2331,25 +3473,25 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="20" t="n">
+      <c r="A80" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="B80" s="21" t="n">
+      <c r="B80" s="11" t="n">
         <v>0.4831</v>
       </c>
-      <c r="C80" s="20" t="n">
+      <c r="C80" s="10" t="n">
         <v>15.507</v>
       </c>
-      <c r="D80" s="21" t="n">
+      <c r="D80" s="11" t="n">
         <v>0.3816</v>
       </c>
-      <c r="E80" s="20" t="n">
+      <c r="E80" s="10" t="n">
         <v>11.448</v>
       </c>
-      <c r="F80" s="21" t="n">
+      <c r="F80" s="11" t="n">
         <v>0.1016</v>
       </c>
-      <c r="G80" s="20" t="n">
+      <c r="G80" s="10" t="n">
         <v>3.048</v>
       </c>
     </row>
@@ -2357,19 +3499,19 @@
       <c r="A81" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="B81" s="11" t="n">
+      <c r="B81" s="9" t="n">
         <v>0.5132</v>
       </c>
       <c r="C81" s="6" t="n">
         <v>14.604</v>
       </c>
-      <c r="D81" s="11" t="n">
+      <c r="D81" s="9" t="n">
         <v>0.3961</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>11.883</v>
       </c>
-      <c r="F81" s="11" t="n">
+      <c r="F81" s="9" t="n">
         <v>0.1172</v>
       </c>
       <c r="G81" s="6" t="n">
@@ -2377,25 +3519,25 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="20" t="n">
+      <c r="A82" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="B82" s="21" t="n">
+      <c r="B82" s="11" t="n">
         <v>0.5416</v>
       </c>
-      <c r="C82" s="20" t="n">
+      <c r="C82" s="10" t="n">
         <v>13.752</v>
       </c>
-      <c r="D82" s="21" t="n">
+      <c r="D82" s="11" t="n">
         <v>0.4083</v>
       </c>
-      <c r="E82" s="20" t="n">
+      <c r="E82" s="10" t="n">
         <v>12.249</v>
       </c>
-      <c r="F82" s="21" t="n">
+      <c r="F82" s="11" t="n">
         <v>0.1333</v>
       </c>
-      <c r="G82" s="20" t="n">
+      <c r="G82" s="10" t="n">
         <v>3.999</v>
       </c>
     </row>
@@ -2403,19 +3545,19 @@
       <c r="A83" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="B83" s="11" t="n">
+      <c r="B83" s="9" t="n">
         <v>0.5683</v>
       </c>
       <c r="C83" s="6" t="n">
         <v>12.951</v>
       </c>
-      <c r="D83" s="11" t="n">
+      <c r="D83" s="9" t="n">
         <v>0.4185</v>
       </c>
       <c r="E83" s="6" t="n">
         <v>12.555</v>
       </c>
-      <c r="F83" s="11" t="n">
+      <c r="F83" s="9" t="n">
         <v>0.1498</v>
       </c>
       <c r="G83" s="6" t="n">
@@ -2423,30 +3565,30 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="n">
+      <c r="A84" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B84" s="21" t="n">
+      <c r="B84" s="11" t="n">
         <v>0.5934</v>
       </c>
-      <c r="C84" s="20" t="n">
+      <c r="C84" s="10" t="n">
         <v>12.198</v>
       </c>
-      <c r="D84" s="21" t="n">
+      <c r="D84" s="11" t="n">
         <v>0.4267</v>
       </c>
-      <c r="E84" s="20" t="n">
+      <c r="E84" s="10" t="n">
         <v>12.801</v>
       </c>
-      <c r="F84" s="21" t="n">
+      <c r="F84" s="11" t="n">
         <v>0.1667</v>
       </c>
-      <c r="G84" s="20" t="n">
+      <c r="G84" s="10" t="n">
         <v>5.000999999999999</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="19" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>Реактор 4</t>
         </is>
@@ -2493,19 +3635,19 @@
       <c r="A89" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B89" s="11" t="n">
+      <c r="B89" s="9" t="n">
         <v>0.5934</v>
       </c>
       <c r="C89" s="6" t="n">
         <v>12.198</v>
       </c>
-      <c r="D89" s="11" t="n">
+      <c r="D89" s="9" t="n">
         <v>0.4267</v>
       </c>
       <c r="E89" s="6" t="n">
         <v>12.801</v>
       </c>
-      <c r="F89" s="11" t="n">
+      <c r="F89" s="9" t="n">
         <v>0.1667</v>
       </c>
       <c r="G89" s="6" t="n">
@@ -2513,25 +3655,25 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="20" t="n">
+      <c r="A90" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="B90" s="21" t="n">
+      <c r="B90" s="11" t="n">
         <v>0.6171</v>
       </c>
-      <c r="C90" s="20" t="n">
+      <c r="C90" s="10" t="n">
         <v>11.487</v>
       </c>
-      <c r="D90" s="21" t="n">
+      <c r="D90" s="11" t="n">
         <v>0.4332</v>
       </c>
-      <c r="E90" s="20" t="n">
+      <c r="E90" s="10" t="n">
         <v>12.996</v>
       </c>
-      <c r="F90" s="21" t="n">
+      <c r="F90" s="11" t="n">
         <v>0.1839</v>
       </c>
-      <c r="G90" s="20" t="n">
+      <c r="G90" s="10" t="n">
         <v>5.517</v>
       </c>
     </row>
@@ -2539,19 +3681,19 @@
       <c r="A91" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="B91" s="11" t="n">
+      <c r="B91" s="9" t="n">
         <v>0.6394</v>
       </c>
       <c r="C91" s="6" t="n">
         <v>10.818</v>
       </c>
-      <c r="D91" s="11" t="n">
+      <c r="D91" s="9" t="n">
         <v>0.4381</v>
       </c>
       <c r="E91" s="6" t="n">
         <v>13.143</v>
       </c>
-      <c r="F91" s="11" t="n">
+      <c r="F91" s="9" t="n">
         <v>0.2013</v>
       </c>
       <c r="G91" s="6" t="n">
@@ -2559,25 +3701,25 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="n">
+      <c r="A92" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="B92" s="21" t="n">
+      <c r="B92" s="11" t="n">
         <v>0.6604</v>
       </c>
-      <c r="C92" s="20" t="n">
+      <c r="C92" s="10" t="n">
         <v>10.188</v>
       </c>
-      <c r="D92" s="21" t="n">
+      <c r="D92" s="11" t="n">
         <v>0.4415</v>
       </c>
-      <c r="E92" s="20" t="n">
+      <c r="E92" s="10" t="n">
         <v>13.245</v>
       </c>
-      <c r="F92" s="21" t="n">
+      <c r="F92" s="11" t="n">
         <v>0.2189</v>
       </c>
-      <c r="G92" s="20" t="n">
+      <c r="G92" s="10" t="n">
         <v>6.567</v>
       </c>
     </row>
@@ -2585,19 +3727,19 @@
       <c r="A93" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="B93" s="11" t="n">
+      <c r="B93" s="9" t="n">
         <v>0.6802</v>
       </c>
       <c r="C93" s="6" t="n">
         <v>9.593999999999999</v>
       </c>
-      <c r="D93" s="11" t="n">
+      <c r="D93" s="9" t="n">
         <v>0.4435</v>
       </c>
       <c r="E93" s="6" t="n">
         <v>13.305</v>
       </c>
-      <c r="F93" s="11" t="n">
+      <c r="F93" s="9" t="n">
         <v>0.2366</v>
       </c>
       <c r="G93" s="6" t="n">
@@ -2605,37 +3747,37 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="20" t="n">
+      <c r="A94" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B94" s="21" t="n">
+      <c r="B94" s="11" t="n">
         <v>0.6988</v>
       </c>
-      <c r="C94" s="20" t="n">
+      <c r="C94" s="10" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D94" s="21" t="n">
+      <c r="D94" s="11" t="n">
         <v>0.4444</v>
       </c>
-      <c r="E94" s="20" t="n">
+      <c r="E94" s="10" t="n">
         <v>13.332</v>
       </c>
-      <c r="F94" s="21" t="n">
+      <c r="F94" s="11" t="n">
         <v>0.2544</v>
       </c>
-      <c r="G94" s="20" t="n">
+      <c r="G94" s="10" t="n">
         <v>7.632000000000001</v>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1">
-      <c r="A97" s="18" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>Система 4. Четыре параллельно соединённых РИВ одинакового объёма, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин).</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>Реактор 1</t>
         </is>
@@ -2682,19 +3824,19 @@
       <c r="A101" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B101" s="11" t="n">
+      <c r="B101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D101" s="11" t="n">
+      <c r="D101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E101" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F101" s="11" t="n">
+      <c r="F101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="6" t="n">
@@ -2702,25 +3844,25 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="20" t="n">
+      <c r="A102" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="B102" s="21" t="n">
+      <c r="B102" s="11" t="n">
         <v>0.1131</v>
       </c>
-      <c r="C102" s="20" t="n">
+      <c r="C102" s="10" t="n">
         <v>26.607</v>
       </c>
-      <c r="D102" s="21" t="n">
+      <c r="D102" s="11" t="n">
         <v>0.1086</v>
       </c>
-      <c r="E102" s="20" t="n">
+      <c r="E102" s="10" t="n">
         <v>3.258</v>
       </c>
-      <c r="F102" s="21" t="n">
+      <c r="F102" s="11" t="n">
         <v>0.0045</v>
       </c>
-      <c r="G102" s="20" t="n">
+      <c r="G102" s="10" t="n">
         <v>0.135</v>
       </c>
     </row>
@@ -2728,19 +3870,19 @@
       <c r="A103" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="B103" s="11" t="n">
+      <c r="B103" s="9" t="n">
         <v>0.2134</v>
       </c>
       <c r="C103" s="6" t="n">
         <v>23.598</v>
       </c>
-      <c r="D103" s="11" t="n">
+      <c r="D103" s="9" t="n">
         <v>0.1965</v>
       </c>
       <c r="E103" s="6" t="n">
         <v>5.895</v>
       </c>
-      <c r="F103" s="11" t="n">
+      <c r="F103" s="9" t="n">
         <v>0.0168</v>
       </c>
       <c r="G103" s="6" t="n">
@@ -2748,25 +3890,25 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="20" t="n">
+      <c r="A104" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="B104" s="21" t="n">
+      <c r="B104" s="11" t="n">
         <v>0.3023</v>
       </c>
-      <c r="C104" s="20" t="n">
+      <c r="C104" s="10" t="n">
         <v>20.931</v>
       </c>
-      <c r="D104" s="21" t="n">
+      <c r="D104" s="11" t="n">
         <v>0.2669</v>
       </c>
-      <c r="E104" s="20" t="n">
+      <c r="E104" s="10" t="n">
         <v>8.007000000000001</v>
       </c>
-      <c r="F104" s="21" t="n">
+      <c r="F104" s="11" t="n">
         <v>0.0355</v>
       </c>
-      <c r="G104" s="20" t="n">
+      <c r="G104" s="10" t="n">
         <v>1.065</v>
       </c>
     </row>
@@ -2774,19 +3916,19 @@
       <c r="A105" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="B105" s="11" t="n">
+      <c r="B105" s="9" t="n">
         <v>0.3812</v>
       </c>
       <c r="C105" s="6" t="n">
         <v>18.564</v>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D105" s="9" t="n">
         <v>0.3221</v>
       </c>
       <c r="E105" s="6" t="n">
         <v>9.663</v>
       </c>
-      <c r="F105" s="11" t="n">
+      <c r="F105" s="9" t="n">
         <v>0.0591</v>
       </c>
       <c r="G105" s="6" t="n">
@@ -2794,25 +3936,25 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="20" t="n">
+      <c r="A106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="21" t="n">
+      <c r="B106" s="11" t="n">
         <v>0.4512</v>
       </c>
-      <c r="C106" s="20" t="n">
+      <c r="C106" s="10" t="n">
         <v>16.464</v>
       </c>
-      <c r="D106" s="21" t="n">
+      <c r="D106" s="11" t="n">
         <v>0.3645</v>
       </c>
-      <c r="E106" s="20" t="n">
+      <c r="E106" s="10" t="n">
         <v>10.935</v>
       </c>
-      <c r="F106" s="21" t="n">
+      <c r="F106" s="11" t="n">
         <v>0.0867</v>
       </c>
-      <c r="G106" s="20" t="n">
+      <c r="G106" s="10" t="n">
         <v>2.601</v>
       </c>
     </row>
@@ -2820,19 +3962,19 @@
       <c r="A107" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="B107" s="11" t="n">
+      <c r="B107" s="9" t="n">
         <v>0.5132</v>
       </c>
       <c r="C107" s="6" t="n">
         <v>14.604</v>
       </c>
-      <c r="D107" s="11" t="n">
+      <c r="D107" s="9" t="n">
         <v>0.3961</v>
       </c>
       <c r="E107" s="6" t="n">
         <v>11.883</v>
       </c>
-      <c r="F107" s="11" t="n">
+      <c r="F107" s="9" t="n">
         <v>0.1172</v>
       </c>
       <c r="G107" s="6" t="n">
@@ -2840,25 +3982,25 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="20" t="n">
+      <c r="A108" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="B108" s="21" t="n">
+      <c r="B108" s="11" t="n">
         <v>0.5683</v>
       </c>
-      <c r="C108" s="20" t="n">
+      <c r="C108" s="10" t="n">
         <v>12.951</v>
       </c>
-      <c r="D108" s="21" t="n">
+      <c r="D108" s="11" t="n">
         <v>0.4185</v>
       </c>
-      <c r="E108" s="20" t="n">
+      <c r="E108" s="10" t="n">
         <v>12.555</v>
       </c>
-      <c r="F108" s="21" t="n">
+      <c r="F108" s="11" t="n">
         <v>0.1498</v>
       </c>
-      <c r="G108" s="20" t="n">
+      <c r="G108" s="10" t="n">
         <v>4.494</v>
       </c>
     </row>
@@ -2866,19 +4008,19 @@
       <c r="A109" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="B109" s="11" t="n">
+      <c r="B109" s="9" t="n">
         <v>0.6171</v>
       </c>
       <c r="C109" s="6" t="n">
         <v>11.487</v>
       </c>
-      <c r="D109" s="11" t="n">
+      <c r="D109" s="9" t="n">
         <v>0.4332</v>
       </c>
       <c r="E109" s="6" t="n">
         <v>12.996</v>
       </c>
-      <c r="F109" s="11" t="n">
+      <c r="F109" s="9" t="n">
         <v>0.1839</v>
       </c>
       <c r="G109" s="6" t="n">
@@ -2886,25 +4028,25 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="20" t="n">
+      <c r="A110" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="B110" s="21" t="n">
+      <c r="B110" s="11" t="n">
         <v>0.6604</v>
       </c>
-      <c r="C110" s="20" t="n">
+      <c r="C110" s="10" t="n">
         <v>10.188</v>
       </c>
-      <c r="D110" s="21" t="n">
+      <c r="D110" s="11" t="n">
         <v>0.4415</v>
       </c>
-      <c r="E110" s="20" t="n">
+      <c r="E110" s="10" t="n">
         <v>13.245</v>
       </c>
-      <c r="F110" s="21" t="n">
+      <c r="F110" s="11" t="n">
         <v>0.2189</v>
       </c>
-      <c r="G110" s="20" t="n">
+      <c r="G110" s="10" t="n">
         <v>6.567</v>
       </c>
     </row>
@@ -2912,19 +4054,19 @@
       <c r="A111" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B111" s="11" t="n">
+      <c r="B111" s="9" t="n">
         <v>0.6988</v>
       </c>
       <c r="C111" s="6" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D111" s="11" t="n">
+      <c r="D111" s="9" t="n">
         <v>0.4444</v>
       </c>
       <c r="E111" s="6" t="n">
         <v>13.332</v>
       </c>
-      <c r="F111" s="11" t="n">
+      <c r="F111" s="9" t="n">
         <v>0.2544</v>
       </c>
       <c r="G111" s="6" t="n">
@@ -2932,7 +4074,7 @@
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="19" t="inlineStr">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>Реактор 2</t>
         </is>
@@ -2979,19 +4121,19 @@
       <c r="A116" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B116" s="11" t="n">
+      <c r="B116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D116" s="11" t="n">
+      <c r="D116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E116" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="11" t="n">
+      <c r="F116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="6" t="n">
@@ -2999,25 +4141,25 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="20" t="n">
+      <c r="A117" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="B117" s="21" t="n">
+      <c r="B117" s="11" t="n">
         <v>0.1131</v>
       </c>
-      <c r="C117" s="20" t="n">
+      <c r="C117" s="10" t="n">
         <v>26.607</v>
       </c>
-      <c r="D117" s="21" t="n">
+      <c r="D117" s="11" t="n">
         <v>0.1086</v>
       </c>
-      <c r="E117" s="20" t="n">
+      <c r="E117" s="10" t="n">
         <v>3.258</v>
       </c>
-      <c r="F117" s="21" t="n">
+      <c r="F117" s="11" t="n">
         <v>0.0045</v>
       </c>
-      <c r="G117" s="20" t="n">
+      <c r="G117" s="10" t="n">
         <v>0.135</v>
       </c>
     </row>
@@ -3025,19 +4167,19 @@
       <c r="A118" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="B118" s="11" t="n">
+      <c r="B118" s="9" t="n">
         <v>0.2134</v>
       </c>
       <c r="C118" s="6" t="n">
         <v>23.598</v>
       </c>
-      <c r="D118" s="11" t="n">
+      <c r="D118" s="9" t="n">
         <v>0.1965</v>
       </c>
       <c r="E118" s="6" t="n">
         <v>5.895</v>
       </c>
-      <c r="F118" s="11" t="n">
+      <c r="F118" s="9" t="n">
         <v>0.0168</v>
       </c>
       <c r="G118" s="6" t="n">
@@ -3045,25 +4187,25 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="20" t="n">
+      <c r="A119" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="B119" s="21" t="n">
+      <c r="B119" s="11" t="n">
         <v>0.3023</v>
       </c>
-      <c r="C119" s="20" t="n">
+      <c r="C119" s="10" t="n">
         <v>20.931</v>
       </c>
-      <c r="D119" s="21" t="n">
+      <c r="D119" s="11" t="n">
         <v>0.2669</v>
       </c>
-      <c r="E119" s="20" t="n">
+      <c r="E119" s="10" t="n">
         <v>8.007000000000001</v>
       </c>
-      <c r="F119" s="21" t="n">
+      <c r="F119" s="11" t="n">
         <v>0.0355</v>
       </c>
-      <c r="G119" s="20" t="n">
+      <c r="G119" s="10" t="n">
         <v>1.065</v>
       </c>
     </row>
@@ -3071,19 +4213,19 @@
       <c r="A120" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="B120" s="11" t="n">
+      <c r="B120" s="9" t="n">
         <v>0.3812</v>
       </c>
       <c r="C120" s="6" t="n">
         <v>18.564</v>
       </c>
-      <c r="D120" s="11" t="n">
+      <c r="D120" s="9" t="n">
         <v>0.3221</v>
       </c>
       <c r="E120" s="6" t="n">
         <v>9.663</v>
       </c>
-      <c r="F120" s="11" t="n">
+      <c r="F120" s="9" t="n">
         <v>0.0591</v>
       </c>
       <c r="G120" s="6" t="n">
@@ -3091,25 +4233,25 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="20" t="n">
+      <c r="A121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B121" s="21" t="n">
+      <c r="B121" s="11" t="n">
         <v>0.4512</v>
       </c>
-      <c r="C121" s="20" t="n">
+      <c r="C121" s="10" t="n">
         <v>16.464</v>
       </c>
-      <c r="D121" s="21" t="n">
+      <c r="D121" s="11" t="n">
         <v>0.3645</v>
       </c>
-      <c r="E121" s="20" t="n">
+      <c r="E121" s="10" t="n">
         <v>10.935</v>
       </c>
-      <c r="F121" s="21" t="n">
+      <c r="F121" s="11" t="n">
         <v>0.0867</v>
       </c>
-      <c r="G121" s="20" t="n">
+      <c r="G121" s="10" t="n">
         <v>2.601</v>
       </c>
     </row>
@@ -3117,19 +4259,19 @@
       <c r="A122" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="B122" s="11" t="n">
+      <c r="B122" s="9" t="n">
         <v>0.5132</v>
       </c>
       <c r="C122" s="6" t="n">
         <v>14.604</v>
       </c>
-      <c r="D122" s="11" t="n">
+      <c r="D122" s="9" t="n">
         <v>0.3961</v>
       </c>
       <c r="E122" s="6" t="n">
         <v>11.883</v>
       </c>
-      <c r="F122" s="11" t="n">
+      <c r="F122" s="9" t="n">
         <v>0.1172</v>
       </c>
       <c r="G122" s="6" t="n">
@@ -3137,25 +4279,25 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="20" t="n">
+      <c r="A123" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="B123" s="21" t="n">
+      <c r="B123" s="11" t="n">
         <v>0.5683</v>
       </c>
-      <c r="C123" s="20" t="n">
+      <c r="C123" s="10" t="n">
         <v>12.951</v>
       </c>
-      <c r="D123" s="21" t="n">
+      <c r="D123" s="11" t="n">
         <v>0.4185</v>
       </c>
-      <c r="E123" s="20" t="n">
+      <c r="E123" s="10" t="n">
         <v>12.555</v>
       </c>
-      <c r="F123" s="21" t="n">
+      <c r="F123" s="11" t="n">
         <v>0.1498</v>
       </c>
-      <c r="G123" s="20" t="n">
+      <c r="G123" s="10" t="n">
         <v>4.494</v>
       </c>
     </row>
@@ -3163,19 +4305,19 @@
       <c r="A124" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="B124" s="11" t="n">
+      <c r="B124" s="9" t="n">
         <v>0.6171</v>
       </c>
       <c r="C124" s="6" t="n">
         <v>11.487</v>
       </c>
-      <c r="D124" s="11" t="n">
+      <c r="D124" s="9" t="n">
         <v>0.4332</v>
       </c>
       <c r="E124" s="6" t="n">
         <v>12.996</v>
       </c>
-      <c r="F124" s="11" t="n">
+      <c r="F124" s="9" t="n">
         <v>0.1839</v>
       </c>
       <c r="G124" s="6" t="n">
@@ -3183,25 +4325,25 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="20" t="n">
+      <c r="A125" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="B125" s="21" t="n">
+      <c r="B125" s="11" t="n">
         <v>0.6604</v>
       </c>
-      <c r="C125" s="20" t="n">
+      <c r="C125" s="10" t="n">
         <v>10.188</v>
       </c>
-      <c r="D125" s="21" t="n">
+      <c r="D125" s="11" t="n">
         <v>0.4415</v>
       </c>
-      <c r="E125" s="20" t="n">
+      <c r="E125" s="10" t="n">
         <v>13.245</v>
       </c>
-      <c r="F125" s="21" t="n">
+      <c r="F125" s="11" t="n">
         <v>0.2189</v>
       </c>
-      <c r="G125" s="20" t="n">
+      <c r="G125" s="10" t="n">
         <v>6.567</v>
       </c>
     </row>
@@ -3209,19 +4351,19 @@
       <c r="A126" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B126" s="11" t="n">
+      <c r="B126" s="9" t="n">
         <v>0.6988</v>
       </c>
       <c r="C126" s="6" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D126" s="11" t="n">
+      <c r="D126" s="9" t="n">
         <v>0.4444</v>
       </c>
       <c r="E126" s="6" t="n">
         <v>13.332</v>
       </c>
-      <c r="F126" s="11" t="n">
+      <c r="F126" s="9" t="n">
         <v>0.2544</v>
       </c>
       <c r="G126" s="6" t="n">
@@ -3229,7 +4371,7 @@
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="19" t="inlineStr">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>Реактор 3</t>
         </is>
@@ -3276,19 +4418,19 @@
       <c r="A131" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B131" s="11" t="n">
+      <c r="B131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C131" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D131" s="11" t="n">
+      <c r="D131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E131" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F131" s="11" t="n">
+      <c r="F131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G131" s="6" t="n">
@@ -3296,25 +4438,25 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="20" t="n">
+      <c r="A132" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="B132" s="21" t="n">
+      <c r="B132" s="11" t="n">
         <v>0.1131</v>
       </c>
-      <c r="C132" s="20" t="n">
+      <c r="C132" s="10" t="n">
         <v>26.607</v>
       </c>
-      <c r="D132" s="21" t="n">
+      <c r="D132" s="11" t="n">
         <v>0.1086</v>
       </c>
-      <c r="E132" s="20" t="n">
+      <c r="E132" s="10" t="n">
         <v>3.258</v>
       </c>
-      <c r="F132" s="21" t="n">
+      <c r="F132" s="11" t="n">
         <v>0.0045</v>
       </c>
-      <c r="G132" s="20" t="n">
+      <c r="G132" s="10" t="n">
         <v>0.135</v>
       </c>
     </row>
@@ -3322,19 +4464,19 @@
       <c r="A133" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="B133" s="11" t="n">
+      <c r="B133" s="9" t="n">
         <v>0.2134</v>
       </c>
       <c r="C133" s="6" t="n">
         <v>23.598</v>
       </c>
-      <c r="D133" s="11" t="n">
+      <c r="D133" s="9" t="n">
         <v>0.1965</v>
       </c>
       <c r="E133" s="6" t="n">
         <v>5.895</v>
       </c>
-      <c r="F133" s="11" t="n">
+      <c r="F133" s="9" t="n">
         <v>0.0168</v>
       </c>
       <c r="G133" s="6" t="n">
@@ -3342,25 +4484,25 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="20" t="n">
+      <c r="A134" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="B134" s="21" t="n">
+      <c r="B134" s="11" t="n">
         <v>0.3023</v>
       </c>
-      <c r="C134" s="20" t="n">
+      <c r="C134" s="10" t="n">
         <v>20.931</v>
       </c>
-      <c r="D134" s="21" t="n">
+      <c r="D134" s="11" t="n">
         <v>0.2669</v>
       </c>
-      <c r="E134" s="20" t="n">
+      <c r="E134" s="10" t="n">
         <v>8.007000000000001</v>
       </c>
-      <c r="F134" s="21" t="n">
+      <c r="F134" s="11" t="n">
         <v>0.0355</v>
       </c>
-      <c r="G134" s="20" t="n">
+      <c r="G134" s="10" t="n">
         <v>1.065</v>
       </c>
     </row>
@@ -3368,19 +4510,19 @@
       <c r="A135" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="B135" s="11" t="n">
+      <c r="B135" s="9" t="n">
         <v>0.3812</v>
       </c>
       <c r="C135" s="6" t="n">
         <v>18.564</v>
       </c>
-      <c r="D135" s="11" t="n">
+      <c r="D135" s="9" t="n">
         <v>0.3221</v>
       </c>
       <c r="E135" s="6" t="n">
         <v>9.663</v>
       </c>
-      <c r="F135" s="11" t="n">
+      <c r="F135" s="9" t="n">
         <v>0.0591</v>
       </c>
       <c r="G135" s="6" t="n">
@@ -3388,25 +4530,25 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="20" t="n">
+      <c r="A136" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B136" s="21" t="n">
+      <c r="B136" s="11" t="n">
         <v>0.4512</v>
       </c>
-      <c r="C136" s="20" t="n">
+      <c r="C136" s="10" t="n">
         <v>16.464</v>
       </c>
-      <c r="D136" s="21" t="n">
+      <c r="D136" s="11" t="n">
         <v>0.3645</v>
       </c>
-      <c r="E136" s="20" t="n">
+      <c r="E136" s="10" t="n">
         <v>10.935</v>
       </c>
-      <c r="F136" s="21" t="n">
+      <c r="F136" s="11" t="n">
         <v>0.0867</v>
       </c>
-      <c r="G136" s="20" t="n">
+      <c r="G136" s="10" t="n">
         <v>2.601</v>
       </c>
     </row>
@@ -3414,19 +4556,19 @@
       <c r="A137" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="B137" s="11" t="n">
+      <c r="B137" s="9" t="n">
         <v>0.5132</v>
       </c>
       <c r="C137" s="6" t="n">
         <v>14.604</v>
       </c>
-      <c r="D137" s="11" t="n">
+      <c r="D137" s="9" t="n">
         <v>0.3961</v>
       </c>
       <c r="E137" s="6" t="n">
         <v>11.883</v>
       </c>
-      <c r="F137" s="11" t="n">
+      <c r="F137" s="9" t="n">
         <v>0.1172</v>
       </c>
       <c r="G137" s="6" t="n">
@@ -3434,25 +4576,25 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="20" t="n">
+      <c r="A138" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="B138" s="21" t="n">
+      <c r="B138" s="11" t="n">
         <v>0.5683</v>
       </c>
-      <c r="C138" s="20" t="n">
+      <c r="C138" s="10" t="n">
         <v>12.951</v>
       </c>
-      <c r="D138" s="21" t="n">
+      <c r="D138" s="11" t="n">
         <v>0.4185</v>
       </c>
-      <c r="E138" s="20" t="n">
+      <c r="E138" s="10" t="n">
         <v>12.555</v>
       </c>
-      <c r="F138" s="21" t="n">
+      <c r="F138" s="11" t="n">
         <v>0.1498</v>
       </c>
-      <c r="G138" s="20" t="n">
+      <c r="G138" s="10" t="n">
         <v>4.494</v>
       </c>
     </row>
@@ -3460,19 +4602,19 @@
       <c r="A139" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="B139" s="11" t="n">
+      <c r="B139" s="9" t="n">
         <v>0.6171</v>
       </c>
       <c r="C139" s="6" t="n">
         <v>11.487</v>
       </c>
-      <c r="D139" s="11" t="n">
+      <c r="D139" s="9" t="n">
         <v>0.4332</v>
       </c>
       <c r="E139" s="6" t="n">
         <v>12.996</v>
       </c>
-      <c r="F139" s="11" t="n">
+      <c r="F139" s="9" t="n">
         <v>0.1839</v>
       </c>
       <c r="G139" s="6" t="n">
@@ -3480,25 +4622,25 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="20" t="n">
+      <c r="A140" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="B140" s="21" t="n">
+      <c r="B140" s="11" t="n">
         <v>0.6604</v>
       </c>
-      <c r="C140" s="20" t="n">
+      <c r="C140" s="10" t="n">
         <v>10.188</v>
       </c>
-      <c r="D140" s="21" t="n">
+      <c r="D140" s="11" t="n">
         <v>0.4415</v>
       </c>
-      <c r="E140" s="20" t="n">
+      <c r="E140" s="10" t="n">
         <v>13.245</v>
       </c>
-      <c r="F140" s="21" t="n">
+      <c r="F140" s="11" t="n">
         <v>0.2189</v>
       </c>
-      <c r="G140" s="20" t="n">
+      <c r="G140" s="10" t="n">
         <v>6.567</v>
       </c>
     </row>
@@ -3506,19 +4648,19 @@
       <c r="A141" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B141" s="11" t="n">
+      <c r="B141" s="9" t="n">
         <v>0.6988</v>
       </c>
       <c r="C141" s="6" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D141" s="11" t="n">
+      <c r="D141" s="9" t="n">
         <v>0.4444</v>
       </c>
       <c r="E141" s="6" t="n">
         <v>13.332</v>
       </c>
-      <c r="F141" s="11" t="n">
+      <c r="F141" s="9" t="n">
         <v>0.2544</v>
       </c>
       <c r="G141" s="6" t="n">
@@ -3526,7 +4668,7 @@
       </c>
     </row>
     <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="19" t="inlineStr">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>Реактор 4</t>
         </is>
@@ -3573,19 +4715,19 @@
       <c r="A146" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B146" s="11" t="n">
+      <c r="B146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="C146" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D146" s="11" t="n">
+      <c r="D146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E146" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F146" s="11" t="n">
+      <c r="F146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="6" t="n">
@@ -3593,25 +4735,25 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="20" t="n">
+      <c r="A147" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="B147" s="21" t="n">
+      <c r="B147" s="11" t="n">
         <v>0.1131</v>
       </c>
-      <c r="C147" s="20" t="n">
+      <c r="C147" s="10" t="n">
         <v>26.607</v>
       </c>
-      <c r="D147" s="21" t="n">
+      <c r="D147" s="11" t="n">
         <v>0.1086</v>
       </c>
-      <c r="E147" s="20" t="n">
+      <c r="E147" s="10" t="n">
         <v>3.258</v>
       </c>
-      <c r="F147" s="21" t="n">
+      <c r="F147" s="11" t="n">
         <v>0.0045</v>
       </c>
-      <c r="G147" s="20" t="n">
+      <c r="G147" s="10" t="n">
         <v>0.135</v>
       </c>
     </row>
@@ -3619,19 +4761,19 @@
       <c r="A148" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="B148" s="11" t="n">
+      <c r="B148" s="9" t="n">
         <v>0.2134</v>
       </c>
       <c r="C148" s="6" t="n">
         <v>23.598</v>
       </c>
-      <c r="D148" s="11" t="n">
+      <c r="D148" s="9" t="n">
         <v>0.1965</v>
       </c>
       <c r="E148" s="6" t="n">
         <v>5.895</v>
       </c>
-      <c r="F148" s="11" t="n">
+      <c r="F148" s="9" t="n">
         <v>0.0168</v>
       </c>
       <c r="G148" s="6" t="n">
@@ -3639,25 +4781,25 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="20" t="n">
+      <c r="A149" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="B149" s="21" t="n">
+      <c r="B149" s="11" t="n">
         <v>0.3023</v>
       </c>
-      <c r="C149" s="20" t="n">
+      <c r="C149" s="10" t="n">
         <v>20.931</v>
       </c>
-      <c r="D149" s="21" t="n">
+      <c r="D149" s="11" t="n">
         <v>0.2669</v>
       </c>
-      <c r="E149" s="20" t="n">
+      <c r="E149" s="10" t="n">
         <v>8.007000000000001</v>
       </c>
-      <c r="F149" s="21" t="n">
+      <c r="F149" s="11" t="n">
         <v>0.0355</v>
       </c>
-      <c r="G149" s="20" t="n">
+      <c r="G149" s="10" t="n">
         <v>1.065</v>
       </c>
     </row>
@@ -3665,19 +4807,19 @@
       <c r="A150" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="B150" s="11" t="n">
+      <c r="B150" s="9" t="n">
         <v>0.3812</v>
       </c>
       <c r="C150" s="6" t="n">
         <v>18.564</v>
       </c>
-      <c r="D150" s="11" t="n">
+      <c r="D150" s="9" t="n">
         <v>0.3221</v>
       </c>
       <c r="E150" s="6" t="n">
         <v>9.663</v>
       </c>
-      <c r="F150" s="11" t="n">
+      <c r="F150" s="9" t="n">
         <v>0.0591</v>
       </c>
       <c r="G150" s="6" t="n">
@@ -3685,25 +4827,25 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="20" t="n">
+      <c r="A151" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B151" s="21" t="n">
+      <c r="B151" s="11" t="n">
         <v>0.4512</v>
       </c>
-      <c r="C151" s="20" t="n">
+      <c r="C151" s="10" t="n">
         <v>16.464</v>
       </c>
-      <c r="D151" s="21" t="n">
+      <c r="D151" s="11" t="n">
         <v>0.3645</v>
       </c>
-      <c r="E151" s="20" t="n">
+      <c r="E151" s="10" t="n">
         <v>10.935</v>
       </c>
-      <c r="F151" s="21" t="n">
+      <c r="F151" s="11" t="n">
         <v>0.0867</v>
       </c>
-      <c r="G151" s="20" t="n">
+      <c r="G151" s="10" t="n">
         <v>2.601</v>
       </c>
     </row>
@@ -3711,19 +4853,19 @@
       <c r="A152" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="B152" s="11" t="n">
+      <c r="B152" s="9" t="n">
         <v>0.5132</v>
       </c>
       <c r="C152" s="6" t="n">
         <v>14.604</v>
       </c>
-      <c r="D152" s="11" t="n">
+      <c r="D152" s="9" t="n">
         <v>0.3961</v>
       </c>
       <c r="E152" s="6" t="n">
         <v>11.883</v>
       </c>
-      <c r="F152" s="11" t="n">
+      <c r="F152" s="9" t="n">
         <v>0.1172</v>
       </c>
       <c r="G152" s="6" t="n">
@@ -3731,25 +4873,25 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="20" t="n">
+      <c r="A153" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="B153" s="21" t="n">
+      <c r="B153" s="11" t="n">
         <v>0.5683</v>
       </c>
-      <c r="C153" s="20" t="n">
+      <c r="C153" s="10" t="n">
         <v>12.951</v>
       </c>
-      <c r="D153" s="21" t="n">
+      <c r="D153" s="11" t="n">
         <v>0.4185</v>
       </c>
-      <c r="E153" s="20" t="n">
+      <c r="E153" s="10" t="n">
         <v>12.555</v>
       </c>
-      <c r="F153" s="21" t="n">
+      <c r="F153" s="11" t="n">
         <v>0.1498</v>
       </c>
-      <c r="G153" s="20" t="n">
+      <c r="G153" s="10" t="n">
         <v>4.494</v>
       </c>
     </row>
@@ -3757,19 +4899,19 @@
       <c r="A154" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="B154" s="11" t="n">
+      <c r="B154" s="9" t="n">
         <v>0.6171</v>
       </c>
       <c r="C154" s="6" t="n">
         <v>11.487</v>
       </c>
-      <c r="D154" s="11" t="n">
+      <c r="D154" s="9" t="n">
         <v>0.4332</v>
       </c>
       <c r="E154" s="6" t="n">
         <v>12.996</v>
       </c>
-      <c r="F154" s="11" t="n">
+      <c r="F154" s="9" t="n">
         <v>0.1839</v>
       </c>
       <c r="G154" s="6" t="n">
@@ -3777,25 +4919,25 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="20" t="n">
+      <c r="A155" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="B155" s="21" t="n">
+      <c r="B155" s="11" t="n">
         <v>0.6604</v>
       </c>
-      <c r="C155" s="20" t="n">
+      <c r="C155" s="10" t="n">
         <v>10.188</v>
       </c>
-      <c r="D155" s="21" t="n">
+      <c r="D155" s="11" t="n">
         <v>0.4415</v>
       </c>
-      <c r="E155" s="20" t="n">
+      <c r="E155" s="10" t="n">
         <v>13.245</v>
       </c>
-      <c r="F155" s="21" t="n">
+      <c r="F155" s="11" t="n">
         <v>0.2189</v>
       </c>
-      <c r="G155" s="20" t="n">
+      <c r="G155" s="10" t="n">
         <v>6.567</v>
       </c>
     </row>
@@ -3803,19 +4945,19 @@
       <c r="A156" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B156" s="11" t="n">
+      <c r="B156" s="9" t="n">
         <v>0.6988</v>
       </c>
       <c r="C156" s="6" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D156" s="11" t="n">
+      <c r="D156" s="9" t="n">
         <v>0.4444</v>
       </c>
       <c r="E156" s="6" t="n">
         <v>13.332</v>
       </c>
-      <c r="F156" s="11" t="n">
+      <c r="F156" s="9" t="n">
         <v>0.2544</v>
       </c>
       <c r="G156" s="6" t="n">
@@ -3876,7 +5018,7 @@
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>ΠR = v0 · CR_вых. v0 системы = 50 л/мин = 3 м³/ч, CR в кмоль/м³ (= моль/л), поэтому ΠR = 3 · CR, кмоль/ч. Для параллельных схем смешение потоков: CR_вых = CR каждого аппарата (нагрузки равны).</t>
         </is>
@@ -3915,15 +5057,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Единичный РИС-н, л/р №3</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="9" t="n">
         <v>0.5454</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="9" t="n">
         <v>0.303</v>
       </c>
       <c r="D6" s="6" t="n">
@@ -3932,22 +5074,22 @@
       <c r="E6" s="6" t="n">
         <v>27.27</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>база для схем 2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Единичный РИВ, л/р №3</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="15" t="n">
         <v>0.6988</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="15" t="n">
         <v>0.4444</v>
       </c>
       <c r="D7" s="16" t="n">
@@ -3956,70 +5098,70 @@
       <c r="E7" s="16" t="n">
         <v>39.996</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>база для схем 3 и 4</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>1. 4 РИС-н последовательно</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="18" t="n">
         <v>0.6498</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="18" t="n">
         <v>0.3964</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="19" t="n">
         <v>11.892</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="19" t="n">
         <v>35.676</v>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>выше единичного РИС-н, ниже РИВ</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>2. 4 РИС-н параллельно</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="18" t="n">
         <v>0.5454</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="18" t="n">
         <v>0.303</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="19" t="n">
         <v>9.09</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="19" t="n">
         <v>27.27</v>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>совпадает с единичным РИС-н</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>3. 4 РИВ последовательно</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="15" t="n">
         <v>0.6988</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="15" t="n">
         <v>0.4444</v>
       </c>
       <c r="D10" s="16" t="n">
@@ -4028,22 +5170,22 @@
       <c r="E10" s="16" t="n">
         <v>39.996</v>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>совпадает с единичным РИВ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>4. 4 РИВ параллельно</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="15" t="n">
         <v>0.6988</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="15" t="n">
         <v>0.4444</v>
       </c>
       <c r="D11" s="16" t="n">
@@ -4052,7 +5194,7 @@
       <c r="E11" s="16" t="n">
         <v>39.996</v>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>совпадает с единичным РИВ</t>
         </is>
@@ -4126,7 +5268,7 @@
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>1. 4 РИС-н последовательно</t>
         </is>
@@ -4134,19 +5276,19 @@
       <c r="B4" s="6" t="n">
         <v>35.68</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Через каждый аппарат идёт полный расход 50 л/мин, четыре перепада складываются — ΔP высокое.</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>ΠR средняя, гидравлика тяжёлая</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>2. 4 РИС-н параллельно</t>
         </is>
@@ -4154,19 +5296,19 @@
       <c r="B5" s="6" t="n">
         <v>27.27</v>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Расход на ветвь 12,5 л/мин, общий ΔP ≈ одной ветви — сопротивление низкое.</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>ΠR как у одного РИС-н, гидравлика лёгкая</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>3. 4 РИВ последовательно</t>
         </is>
@@ -4174,19 +5316,19 @@
       <c r="B6" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Полный расход 50 л/мин через все четыре РИВ, ΔP максимальное среди схем.</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>ΠR максимальная, гидравлика самая тяжёлая</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>4. 4 РИВ параллельно</t>
         </is>
@@ -4194,12 +5336,12 @@
       <c r="B7" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Расход 12,5 л/мин на ветвь, ΔP как у одного РИВ малого расхода — ниже, чем в ряду.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>ΠR максимальная при меньшем ΔP — предпочтительная схема</t>
         </is>

--- a/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
+++ b/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -700,24 +700,24 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>CA = CA0 · (1 − X)     — непрореагировавший реагент A
 CR = CA0 · Y          — целевой продукт R
 CS = CA0 · Z          — побочный продукт S
-CA0 = 30 моль/л  (вариант 2).  k1 = 0,6 мин⁻¹, k2 = 0,4 мин⁻¹ (л/р №3, n1 = n2 = 1).
-VΣ = 100 л, v0 = 50 л/мин, 4 аппарата по Vi = 25 л.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1"/>
-    <row r="6" ht="20" customHeight="1"/>
-    <row r="7" ht="20" customHeight="1"/>
+CA0 = 30 моль/л. На экране 8 строк (вход и выход каждого из 4 РИС-н), но вход следующего аппарата совпадает с выходом предыдущего, поэтому уникальных состояний пять.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1"/>
+    <row r="6" ht="18" customHeight="1"/>
+    <row r="7" ht="18" customHeight="1"/>
+    <row r="8" ht="18" customHeight="1"/>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Реактор 1, вход (τ = 0; с экрана):</t>
+          <t>Вход в систему / вход реактора 1 (τ = 0):</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Реактор 1, выход (τ = 0,5; с экрана):</t>
+          <t>Выход реактора 1 (τ = 0,5) — он же вход реактора 2:</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Реактор 2, вход (τ = 0; с экрана):</t>
+          <t>Выход реактора 2 (τ = 0,5) — он же вход реактора 3:</t>
         </is>
       </c>
     </row>
@@ -979,16 +979,16 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>X = 0,2308</t>
+          <t>X = 0,4083</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>30·(1−0,2308)</t>
+          <t>30·(1−0,4083)</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>23.076</v>
+        <v>17.751</v>
       </c>
     </row>
     <row r="26">
@@ -1004,16 +1004,16 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Y = 0,1923</t>
+          <t>Y = 0,3082</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>30·0,1923</t>
+          <t>30·0,3082</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>5.769</v>
+        <v>9.245999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1029,22 +1029,22 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Z = 0,0385</t>
+          <t>Z = 0,1001</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>30·0,0385</t>
+          <t>30·0,1001</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1.155</v>
+        <v>3.003</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Реактор 2, выход (τ = 0,5; с экрана):</t>
+          <t>Выход реактора 3 (τ = 0,5) — он же вход реактора 4:</t>
         </is>
       </c>
     </row>
@@ -1088,16 +1088,16 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>X = 0,4083</t>
+          <t>X = 0,5448</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>30·(1−0,4083)</t>
+          <t>30·(1−0,5448)</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>17.751</v>
+        <v>13.656</v>
       </c>
     </row>
     <row r="33">
@@ -1113,16 +1113,16 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Y = 0,3082</t>
+          <t>Y = 0,3706</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>30·0,3082</t>
+          <t>30·0,3706</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>9.245999999999999</v>
+        <v>11.118</v>
       </c>
     </row>
     <row r="34">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Z = 0,1001</t>
+          <t>Z = 0,1742</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>30·0,1001</t>
+          <t>30·0,1742</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>3.003</v>
+        <v>5.226</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Реактор 3, вход (τ = 0; с экрана):</t>
+          <t>Выход реактора 4 (τ = 0,5) — выход системы 1:</t>
         </is>
       </c>
     </row>
@@ -1197,16 +1197,16 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>X = 0,4083</t>
+          <t>X = 0,6498</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>30·(1−0,4083)</t>
+          <t>30·(1−0,6498)</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>17.751</v>
+        <v>10.506</v>
       </c>
     </row>
     <row r="40">
@@ -1222,16 +1222,16 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Y = 0,3082</t>
+          <t>Y = 0,3964</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>30·0,3082</t>
+          <t>30·0,3964</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>9.245999999999999</v>
+        <v>11.892</v>
       </c>
     </row>
     <row r="41">
@@ -1247,1026 +1247,36 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Z = 0,1001</t>
+          <t>Z = 0,2535</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>30·0,1001</t>
+          <t>30·0,2535</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>3.003</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Реактор 3, выход (τ = 0,5; с экрана):</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,5448</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,5448)</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="n">
-        <v>13.656</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,3706</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>30·0,3706</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>11.118</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,1742</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>30·0,1742</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>5.226</v>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Реактор 4, вход (τ = 0; с экрана):</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,5448</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,5448)</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>13.656</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,3706</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>30·0,3706</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="n">
-        <v>11.118</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,1742</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>30·0,1742</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>5.226</v>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Реактор 4, выход (τ = 0,5; выход системы 1, с экрана):</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,6498</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,6498)</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>10.506</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,3964</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>30·0,3964</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>11.892</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,2535</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>30·0,2535</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="n">
         <v>7.605</v>
       </c>
     </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Система 2, каждый из 4 параллельных РИС-н / выход (τi = 2 мин):</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,5454</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,5454)</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>13.638</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,3030</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>30·0,3030</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>9.09</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,2424</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>30·0,2424</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>7.272</v>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Система 3, выход 1-го РИВ (τi = 0,5 мин):</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,2592</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,2592)</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="n">
-        <v>22.224</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,2337</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>30·0,2337</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="n">
-        <v>7.011</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,0254</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>30·0,0254</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="n">
-        <v>0.762</v>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Система 3, выход 2-го РИВ:</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,4512</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,4512)</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="n">
-        <v>16.464</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,3645</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>30·0,3645</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="n">
-        <v>10.935</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,0867</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>30·0,0867</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Система 3, выход 3-го РИВ:</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,5934</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,5934)</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="n">
-        <v>12.198</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,4267</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>30·0,4267</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="n">
-        <v>12.801</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,1667</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>30·0,1667</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="n">
-        <v>5.000999999999999</v>
-      </c>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Система 3, выход 4-го РИВ — выход системы:</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,6988</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,6988)</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="n">
-        <v>9.036000000000001</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,4444</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>30·0,4444</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="n">
-        <v>13.332</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,2544</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>30·0,2544</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="n">
-        <v>7.632000000000001</v>
-      </c>
-    </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Система 4, каждый из 4 параллельных РИВ / выход (τi = 2 мин):</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>Величина</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Формула</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>С экрана</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>Подстановка</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Результат, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>CA0·(1−X)</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>X = 0,6988</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>30·(1−0,6988)</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="n">
-        <v>9.036000000000001</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Y</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>Y = 0,4444</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>30·0,4444</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="n">
-        <v>13.332</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>CA0·Z</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>Z = 0,2544</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>30·0,2544</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="n">
-        <v>7.632000000000001</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Проверка: CA + CR + CS = CA0, то есть (1−X) + Y + Z = 1. Расхождения в 0,01 моль/л — округление X, Y, Z на экране. Дальше все таблицы пункта 2 считаются этими же формулами.</t>
         </is>
       </c>
     </row>
-    <row r="108"/>
-    <row r="109"/>
+    <row r="45"/>
+    <row r="46"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="A4:H7"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A58:G58"/>
+  <mergeCells count="9">
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A79:G79"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A100:G100"/>
+    <mergeCell ref="A4:H8"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A107:H109"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A44:H46"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>

--- a/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
+++ b/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1687,7 +1687,7 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Реактор 1</t>
+          <t>Реакторы 1–4 (одинаковые)</t>
         </is>
       </c>
     </row>
@@ -1774,190 +1774,199 @@
         <v>7.272</v>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Система 3. Четыре последовательно соединённых РИВ одинакового объёма (vi = 50 л/мин, τi = 0,5 мин).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
+    <row r="41">
+      <c r="A41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B39" s="9" t="n">
+      <c r="B41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C41" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="D41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G41" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>0.5454</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>13.638</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>0.2424</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>7.272</v>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>28.254</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>1.713</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>26.607</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>3.258</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>25.059</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>0.294</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>0</v>
+        <v>0.2134</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>30</v>
+        <v>23.598</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0</v>
+        <v>0.1965</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0</v>
+        <v>5.895</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>0</v>
+        <v>0.0168</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B46" s="11" t="n">
-        <v>0.5454</v>
+        <v>0.2592</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>13.638</v>
+        <v>22.224</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.303</v>
+        <v>0.2337</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>9.09</v>
+        <v>7.011</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.2424</v>
+        <v>0.0254</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>7.272</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Реактор 4</t>
+          <t>Реактор 2</t>
         </is>
       </c>
     </row>
@@ -2003,716 +2012,764 @@
         <v>0</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>0</v>
+        <v>0.2592</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>30</v>
+        <v>22.224</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0</v>
+        <v>0.2337</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>7.011</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>0</v>
+        <v>0.0254</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="B52" s="11" t="n">
-        <v>0.5454</v>
+        <v>0.3023</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>13.638</v>
+        <v>20.931</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>0.303</v>
+        <v>0.2669</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>9.09</v>
+        <v>8.007000000000001</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>0.2424</v>
+        <v>0.0355</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>7.272</v>
-      </c>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Система 3. Четыре последовательно соединённых РИВ одинакового объёма (vi = 50 л/мин, τi = 0,5 мин).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+        <v>1.065</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>8.886000000000001</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>1.401</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>18.564</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>9.663</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>1.773</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>17.481</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>10.344</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>2.175</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>16.464</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>10.935</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>2.601</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B60" s="11" t="n">
-        <v>0.0582</v>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>28.254</v>
-      </c>
-      <c r="D60" s="11" t="n">
-        <v>0.0571</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>1.713</v>
-      </c>
-      <c r="F60" s="11" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="G60" s="10" t="n">
-        <v>0.036</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>0.1131</v>
+        <v>0.4512</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>26.607</v>
+        <v>16.464</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.1086</v>
+        <v>0.3645</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>3.258</v>
+        <v>10.935</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>0.0045</v>
+        <v>0.0867</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.135</v>
+        <v>2.601</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="B62" s="11" t="n">
-        <v>0.1647</v>
+        <v>0.4831</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>25.059</v>
+        <v>15.507</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>0.155</v>
+        <v>0.3816</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>4.65</v>
+        <v>11.448</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>0.0098</v>
+        <v>0.1016</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>0.294</v>
+        <v>3.048</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="B63" s="9" t="n">
-        <v>0.2134</v>
+        <v>0.5132</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>23.598</v>
+        <v>14.604</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.1965</v>
+        <v>0.3961</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>5.895</v>
+        <v>11.883</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>0.0168</v>
+        <v>0.1172</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>0.504</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>0.5416</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>13.752</v>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>12.249</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>3.999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>12.951</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>12.555</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>4.494</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B64" s="11" t="n">
-        <v>0.2592</v>
-      </c>
-      <c r="C64" s="10" t="n">
-        <v>22.224</v>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>0.2337</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>7.011</v>
-      </c>
-      <c r="F64" s="11" t="n">
-        <v>0.0254</v>
-      </c>
-      <c r="G64" s="10" t="n">
-        <v>0.762</v>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="B66" s="11" t="n">
+        <v>0.5934</v>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>12.198</v>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>12.801</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>5.000999999999999</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B69" s="9" t="n">
-        <v>0.2592</v>
-      </c>
-      <c r="C69" s="6" t="n">
-        <v>22.224</v>
-      </c>
-      <c r="D69" s="9" t="n">
-        <v>0.2337</v>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>7.011</v>
-      </c>
-      <c r="F69" s="9" t="n">
-        <v>0.0254</v>
-      </c>
-      <c r="G69" s="6" t="n">
-        <v>0.762</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B70" s="11" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C70" s="10" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D70" s="11" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F70" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G70" s="10" t="n">
-        <v>1.065</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>0.343</v>
+        <v>0.5934</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>19.71</v>
+        <v>12.198</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.2962</v>
+        <v>0.4267</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>8.886000000000001</v>
+        <v>12.801</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>0.0467</v>
+        <v>0.1667</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>1.401</v>
+        <v>5.000999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="B72" s="11" t="n">
-        <v>0.3812</v>
+        <v>0.6171</v>
       </c>
       <c r="C72" s="10" t="n">
-        <v>18.564</v>
+        <v>11.487</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>0.3221</v>
+        <v>0.4332</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>9.663</v>
+        <v>12.996</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>0.0591</v>
+        <v>0.1839</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>1.773</v>
+        <v>5.517</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="B73" s="9" t="n">
-        <v>0.4173</v>
+        <v>0.6394</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>17.481</v>
+        <v>10.818</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.3448</v>
+        <v>0.4381</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>10.344</v>
+        <v>13.143</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>0.0725</v>
+        <v>0.2013</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>2.175</v>
+        <v>6.039000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>10.188</v>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>13.245</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>6.567</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>0.6802</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>9.593999999999999</v>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>13.305</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>7.098</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B74" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C74" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D74" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F74" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G74" s="10" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="B76" s="11" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="C76" s="10" t="n">
+        <v>9.036000000000001</v>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>13.332</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>7.632000000000001</v>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Система 4. Четыре параллельно соединённых РИВ одинакового объёма, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Реакторы 1–4 (одинаковые)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B79" s="9" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C79" s="6" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D79" s="9" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E79" s="6" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F79" s="9" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G79" s="6" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B80" s="11" t="n">
-        <v>0.4831</v>
-      </c>
-      <c r="C80" s="10" t="n">
-        <v>15.507</v>
-      </c>
-      <c r="D80" s="11" t="n">
-        <v>0.3816</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>11.448</v>
-      </c>
-      <c r="F80" s="11" t="n">
-        <v>0.1016</v>
-      </c>
-      <c r="G80" s="10" t="n">
-        <v>3.048</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B81" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C81" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E81" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F81" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G81" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B82" s="11" t="n">
-        <v>0.5416</v>
-      </c>
-      <c r="C82" s="10" t="n">
-        <v>13.752</v>
-      </c>
-      <c r="D82" s="11" t="n">
-        <v>0.4083</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>12.249</v>
-      </c>
-      <c r="F82" s="11" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="G82" s="10" t="n">
-        <v>3.999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>0.5683</v>
+        <v>0</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>12.951</v>
+        <v>30</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.4185</v>
+        <v>0</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>12.555</v>
+        <v>0</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>0.1498</v>
+        <v>0</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>4.494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="B84" s="11" t="n">
-        <v>0.5934</v>
+        <v>0.1131</v>
       </c>
       <c r="C84" s="10" t="n">
-        <v>12.198</v>
+        <v>26.607</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>0.4267</v>
+        <v>0.1086</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>12.801</v>
+        <v>3.258</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>0.1667</v>
+        <v>0.0045</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>5.000999999999999</v>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="28" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>23.598</v>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>0.504</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B86" s="11" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>20.931</v>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>8.007000000000001</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>1.065</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>18.564</v>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>9.663</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>1.773</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>16.464</v>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>10.935</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>2.601</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>0.5934</v>
+        <v>0.5132</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>12.198</v>
+        <v>14.604</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.4267</v>
+        <v>0.3961</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>12.801</v>
+        <v>11.883</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>0.1667</v>
+        <v>0.1172</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>5.000999999999999</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="B90" s="11" t="n">
-        <v>0.6171</v>
+        <v>0.5683</v>
       </c>
       <c r="C90" s="10" t="n">
-        <v>11.487</v>
+        <v>12.951</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>0.4332</v>
+        <v>0.4185</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>12.996</v>
+        <v>12.555</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>0.1839</v>
+        <v>0.1498</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>5.517</v>
+        <v>4.494</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>0.6394</v>
+        <v>0.6171</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>10.818</v>
+        <v>11.487</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.4381</v>
+        <v>0.4332</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>13.143</v>
+        <v>12.996</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>0.2013</v>
+        <v>0.1839</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>6.039000000000001</v>
+        <v>5.517</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="B92" s="11" t="n">
         <v>0.6604</v>
@@ -2735,1266 +2792,42 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>0.6802</v>
+        <v>0.6988</v>
       </c>
       <c r="C93" s="6" t="n">
-        <v>9.593999999999999</v>
+        <v>9.036000000000001</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.4435</v>
+        <v>0.4444</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>13.305</v>
+        <v>13.332</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>0.2366</v>
+        <v>0.2544</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>7.098</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B94" s="11" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="C94" s="10" t="n">
-        <v>9.036000000000001</v>
-      </c>
-      <c r="D94" s="11" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="F94" s="11" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="G94" s="10" t="n">
         <v>7.632000000000001</v>
       </c>
     </row>
-    <row r="97" ht="24" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>Система 4. Четыре параллельно соединённых РИВ одинакового объёма, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин).</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B102" s="11" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C102" s="10" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D102" s="11" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>3.258</v>
-      </c>
-      <c r="F102" s="11" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G102" s="10" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B103" s="9" t="n">
-        <v>0.2134</v>
-      </c>
-      <c r="C103" s="6" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="D103" s="9" t="n">
-        <v>0.1965</v>
-      </c>
-      <c r="E103" s="6" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="F103" s="9" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="G103" s="6" t="n">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B104" s="11" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C104" s="10" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D104" s="11" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F104" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G104" s="10" t="n">
-        <v>1.065</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B105" s="9" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C105" s="6" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D105" s="9" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E105" s="6" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F105" s="9" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G105" s="6" t="n">
-        <v>1.773</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B106" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C106" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D106" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F106" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G106" s="10" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B107" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C107" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D107" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E107" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F107" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G107" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B108" s="11" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C108" s="10" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D108" s="11" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F108" s="11" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G108" s="10" t="n">
-        <v>4.494</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B109" s="9" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C109" s="6" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D109" s="9" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E109" s="6" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F109" s="9" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G109" s="6" t="n">
-        <v>5.517</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B110" s="11" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C110" s="10" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D110" s="11" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F110" s="11" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G110" s="10" t="n">
-        <v>6.567</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B111" s="9" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="C111" s="6" t="n">
-        <v>9.036000000000001</v>
-      </c>
-      <c r="D111" s="9" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E111" s="6" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="F111" s="9" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="G111" s="6" t="n">
-        <v>7.632000000000001</v>
-      </c>
-    </row>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B117" s="11" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C117" s="10" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D117" s="11" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>3.258</v>
-      </c>
-      <c r="F117" s="11" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G117" s="10" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B118" s="9" t="n">
-        <v>0.2134</v>
-      </c>
-      <c r="C118" s="6" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="D118" s="9" t="n">
-        <v>0.1965</v>
-      </c>
-      <c r="E118" s="6" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="F118" s="9" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="G118" s="6" t="n">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B119" s="11" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C119" s="10" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D119" s="11" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F119" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G119" s="10" t="n">
-        <v>1.065</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B120" s="9" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C120" s="6" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D120" s="9" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E120" s="6" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G120" s="6" t="n">
-        <v>1.773</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B121" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C121" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D121" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F121" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G121" s="10" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B122" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C122" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D122" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E122" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F122" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G122" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B123" s="11" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C123" s="10" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D123" s="11" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F123" s="11" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G123" s="10" t="n">
-        <v>4.494</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B124" s="9" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C124" s="6" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D124" s="9" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E124" s="6" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F124" s="9" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G124" s="6" t="n">
-        <v>5.517</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B125" s="11" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C125" s="10" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D125" s="11" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F125" s="11" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G125" s="10" t="n">
-        <v>6.567</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B126" s="9" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="C126" s="6" t="n">
-        <v>9.036000000000001</v>
-      </c>
-      <c r="D126" s="9" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E126" s="6" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="F126" s="9" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="G126" s="6" t="n">
-        <v>7.632000000000001</v>
-      </c>
-    </row>
-    <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G130" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B132" s="11" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C132" s="10" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D132" s="11" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>3.258</v>
-      </c>
-      <c r="F132" s="11" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G132" s="10" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B133" s="9" t="n">
-        <v>0.2134</v>
-      </c>
-      <c r="C133" s="6" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="D133" s="9" t="n">
-        <v>0.1965</v>
-      </c>
-      <c r="E133" s="6" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="G133" s="6" t="n">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B134" s="11" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C134" s="10" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D134" s="11" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F134" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G134" s="10" t="n">
-        <v>1.065</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B135" s="9" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C135" s="6" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D135" s="9" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E135" s="6" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F135" s="9" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G135" s="6" t="n">
-        <v>1.773</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B136" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C136" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D136" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F136" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G136" s="10" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B137" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C137" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D137" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E137" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F137" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G137" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B138" s="11" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C138" s="10" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D138" s="11" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F138" s="11" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G138" s="10" t="n">
-        <v>4.494</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B139" s="9" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C139" s="6" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D139" s="9" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E139" s="6" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F139" s="9" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G139" s="6" t="n">
-        <v>5.517</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B140" s="11" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C140" s="10" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D140" s="11" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F140" s="11" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G140" s="10" t="n">
-        <v>6.567</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B141" s="9" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="C141" s="6" t="n">
-        <v>9.036000000000001</v>
-      </c>
-      <c r="D141" s="9" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E141" s="6" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="F141" s="9" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="G141" s="6" t="n">
-        <v>7.632000000000001</v>
-      </c>
-    </row>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="28" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G145" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C146" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B147" s="11" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C147" s="10" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D147" s="11" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>3.258</v>
-      </c>
-      <c r="F147" s="11" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G147" s="10" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B148" s="9" t="n">
-        <v>0.2134</v>
-      </c>
-      <c r="C148" s="6" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="D148" s="9" t="n">
-        <v>0.1965</v>
-      </c>
-      <c r="E148" s="6" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="F148" s="9" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="G148" s="6" t="n">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B149" s="11" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C149" s="10" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D149" s="11" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F149" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G149" s="10" t="n">
-        <v>1.065</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B150" s="9" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C150" s="6" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D150" s="9" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E150" s="6" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F150" s="9" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G150" s="6" t="n">
-        <v>1.773</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B151" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C151" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D151" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F151" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G151" s="10" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B152" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C152" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D152" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E152" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F152" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G152" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B153" s="11" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C153" s="10" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D153" s="11" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F153" s="11" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G153" s="10" t="n">
-        <v>4.494</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B154" s="9" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C154" s="6" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D154" s="9" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E154" s="6" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F154" s="9" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G154" s="6" t="n">
-        <v>5.517</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B155" s="11" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C155" s="10" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D155" s="11" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F155" s="11" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G155" s="10" t="n">
-        <v>6.567</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B156" s="9" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="C156" s="6" t="n">
-        <v>9.036000000000001</v>
-      </c>
-      <c r="D156" s="9" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E156" s="6" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="F156" s="9" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="G156" s="6" t="n">
-        <v>7.632000000000001</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A97:G97"/>
+  <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A69:G69"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A114:G114"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A81:G81"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A99:G99"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A129:G129"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>

--- a/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
+++ b/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1306,21 +1306,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Пункт 2. Таблицы моделирования для каждого реактора каждой системы</t>
+          <t>Пункт 2. Четыре таблицы — по одной на каждую исследуемую систему</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Система 1. Четыре последовательно соединённых РИС-н одинакового объёма  (vi = 50 л/мин, τi = 0,5 мин). Экран программы.</t>
+          <t>Таблица 1. Система 1 — четыре РИС-н последовательно (vi = 50 л/мин, τi = 0,5 мин). Вход и выходы реакторов 1–4, экран программы.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Реактор 1</t>
+          <t>Система 1</t>
         </is>
       </c>
     </row>
@@ -1407,514 +1407,571 @@
         <v>1.155</v>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>17.751</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>9.245999999999999</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3.003</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>13.656</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>11.118</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>5.226</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>10.506</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>11.892</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>7.605</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Таблица 2. Система 2 — четыре РИС-н параллельно (vi = 12,5 л/мин, τi = 2 мин). Аппараты одинаковы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Система 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
+    <row r="18">
+      <c r="A18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>23.076</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0.1923</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>5.769</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>1.155</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>0.4083</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>17.751</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>0.3082</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>9.245999999999999</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>0.1001</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>3.003</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>13.638</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>7.272</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Таблица 3. Система 3 — четыре РИВ последовательно (vi = 50 л/мин, Στ = 2 мин). Эквивалентно одному РИВ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Система 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="n">
+    <row r="26">
+      <c r="A26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>0.4083</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>17.751</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>0.3082</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>9.245999999999999</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0.1001</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>3.003</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>0.5448</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>13.656</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>0.3706</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>11.118</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>0.1742</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>5.226</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="B26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>26.607</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>3.258</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>23.598</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0.504</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>20.931</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>8.007000000000001</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>1.065</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>18.564</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>9.663</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>1.773</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>16.464</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>10.935</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>2.601</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>14.604</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>11.883</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>3.516</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>12.951</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>12.555</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>4.494</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>0.6171</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>11.487</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>12.996</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>5.517</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>10.188</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>13.245</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>6.567</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>9.036000000000001</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>13.332</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>7.632000000000001</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Таблица 4. Система 4 — четыре РИВ параллельно (vi = 12,5 л/мин, τi = 2 мин). Выход как у единичного РИВ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Система 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>0.5448</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>13.656</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>0.3706</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>11.118</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.1742</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>5.226</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>0.6498</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>10.506</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>0.3964</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>11.892</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>0.2535</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>7.605</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Система 2. Четыре параллельно соединённых РИС-н одинакового объёма, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Реакторы 1–4 (одинаковые)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>0.5454</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>13.638</v>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>0.2424</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>7.272</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Система 3. Четыре последовательно соединённых РИВ одинакового объёма (vi = 50 л/мин, τi = 0,5 мин).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>0.0582</v>
-      </c>
-      <c r="C42" s="10" t="n">
-        <v>28.254</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>0.0571</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>1.713</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>0.036</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>0.1131</v>
+        <v>0</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>26.607</v>
+        <v>30</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.1086</v>
+        <v>0</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>3.258</v>
+        <v>0</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0.0045</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="B44" s="11" t="n">
-        <v>0.1647</v>
+        <v>0.1131</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>25.059</v>
+        <v>26.607</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.155</v>
+        <v>0.1086</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>4.65</v>
+        <v>3.258</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.0098</v>
+        <v>0.0045</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>0.294</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="45">
@@ -1942,894 +1999,199 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="B46" s="11" t="n">
-        <v>0.2592</v>
+        <v>0.3023</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>22.224</v>
+        <v>20.931</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.2337</v>
+        <v>0.2669</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>7.011</v>
+        <v>8.007000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.0254</v>
+        <v>0.0355</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>0.762</v>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
+        <v>1.065</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>18.564</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>9.663</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>1.773</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>16.464</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>10.935</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>2.601</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>14.604</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>11.883</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>3.516</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>12.951</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>12.555</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>4.494</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>0.2592</v>
+        <v>0.6171</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>22.224</v>
+        <v>11.487</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.2337</v>
+        <v>0.4332</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>7.011</v>
+        <v>12.996</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>0.0254</v>
+        <v>0.1839</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.762</v>
+        <v>5.517</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="B52" s="11" t="n">
-        <v>0.3023</v>
+        <v>0.6604</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>20.931</v>
+        <v>10.188</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>0.2669</v>
+        <v>0.4415</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>8.007000000000001</v>
+        <v>13.245</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>0.0355</v>
+        <v>0.2189</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>1.065</v>
+        <v>6.567</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>0.343</v>
+        <v>0.6988</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>19.71</v>
+        <v>9.036000000000001</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.2962</v>
+        <v>0.4444</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>8.886000000000001</v>
+        <v>13.332</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>0.0467</v>
+        <v>0.2544</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>1.401</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B54" s="11" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D54" s="11" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F54" s="11" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G54" s="10" t="n">
-        <v>1.773</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B55" s="9" t="n">
-        <v>0.4173</v>
-      </c>
-      <c r="C55" s="6" t="n">
-        <v>17.481</v>
-      </c>
-      <c r="D55" s="9" t="n">
-        <v>0.3448</v>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>10.344</v>
-      </c>
-      <c r="F55" s="9" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>2.175</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D56" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F56" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G56" s="10" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B61" s="9" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D61" s="9" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F61" s="9" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B62" s="11" t="n">
-        <v>0.4831</v>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>15.507</v>
-      </c>
-      <c r="D62" s="11" t="n">
-        <v>0.3816</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>11.448</v>
-      </c>
-      <c r="F62" s="11" t="n">
-        <v>0.1016</v>
-      </c>
-      <c r="G62" s="10" t="n">
-        <v>3.048</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B63" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C63" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D63" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>0.5416</v>
-      </c>
-      <c r="C64" s="10" t="n">
-        <v>13.752</v>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>0.4083</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>12.249</v>
-      </c>
-      <c r="F64" s="11" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="G64" s="10" t="n">
-        <v>3.999</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B65" s="9" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C65" s="6" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D65" s="9" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F65" s="9" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>4.494</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B66" s="11" t="n">
-        <v>0.5934</v>
-      </c>
-      <c r="C66" s="10" t="n">
-        <v>12.198</v>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>0.4267</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>12.801</v>
-      </c>
-      <c r="F66" s="11" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="G66" s="10" t="n">
-        <v>5.000999999999999</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>Реактор 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B71" s="9" t="n">
-        <v>0.5934</v>
-      </c>
-      <c r="C71" s="6" t="n">
-        <v>12.198</v>
-      </c>
-      <c r="D71" s="9" t="n">
-        <v>0.4267</v>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>12.801</v>
-      </c>
-      <c r="F71" s="9" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="G71" s="6" t="n">
-        <v>5.000999999999999</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B72" s="11" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C72" s="10" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D72" s="11" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F72" s="11" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G72" s="10" t="n">
-        <v>5.517</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B73" s="9" t="n">
-        <v>0.6394</v>
-      </c>
-      <c r="C73" s="6" t="n">
-        <v>10.818</v>
-      </c>
-      <c r="D73" s="9" t="n">
-        <v>0.4381</v>
-      </c>
-      <c r="E73" s="6" t="n">
-        <v>13.143</v>
-      </c>
-      <c r="F73" s="9" t="n">
-        <v>0.2013</v>
-      </c>
-      <c r="G73" s="6" t="n">
-        <v>6.039000000000001</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B74" s="11" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C74" s="10" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D74" s="11" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F74" s="11" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G74" s="10" t="n">
-        <v>6.567</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B75" s="9" t="n">
-        <v>0.6802</v>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>9.593999999999999</v>
-      </c>
-      <c r="D75" s="9" t="n">
-        <v>0.4435</v>
-      </c>
-      <c r="E75" s="6" t="n">
-        <v>13.305</v>
-      </c>
-      <c r="F75" s="9" t="n">
-        <v>0.2366</v>
-      </c>
-      <c r="G75" s="6" t="n">
-        <v>7.098</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B76" s="11" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="C76" s="10" t="n">
-        <v>9.036000000000001</v>
-      </c>
-      <c r="D76" s="11" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="F76" s="11" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="G76" s="10" t="n">
         <v>7.632000000000001</v>
       </c>
     </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Система 4. Четыре параллельно соединённых РИВ одинакового объёма, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Реакторы 1–4 (одинаковые)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B84" s="11" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D84" s="11" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>3.258</v>
-      </c>
-      <c r="F84" s="11" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G84" s="10" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B85" s="9" t="n">
-        <v>0.2134</v>
-      </c>
-      <c r="C85" s="6" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="D85" s="9" t="n">
-        <v>0.1965</v>
-      </c>
-      <c r="E85" s="6" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="F85" s="9" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="G85" s="6" t="n">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B86" s="11" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C86" s="10" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D86" s="11" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F86" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G86" s="10" t="n">
-        <v>1.065</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B87" s="9" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C87" s="6" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D87" s="9" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E87" s="6" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F87" s="9" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G87" s="6" t="n">
-        <v>1.773</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B88" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C88" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D88" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F88" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G88" s="10" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B89" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C89" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D89" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E89" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F89" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G89" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B90" s="11" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C90" s="10" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D90" s="11" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F90" s="11" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G90" s="10" t="n">
-        <v>4.494</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B91" s="9" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C91" s="6" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D91" s="9" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E91" s="6" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F91" s="9" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G91" s="6" t="n">
-        <v>5.517</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B92" s="11" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C92" s="10" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D92" s="11" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F92" s="11" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G92" s="10" t="n">
-        <v>6.567</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B93" s="9" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="C93" s="6" t="n">
-        <v>9.036000000000001</v>
-      </c>
-      <c r="D93" s="9" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E93" s="6" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="F93" s="9" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="G93" s="6" t="n">
-        <v>7.632000000000001</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="9">
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
+++ b/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1313,7 +1313,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Таблица 1. Система 1 — четыре РИС-н последовательно (vi = 50 л/мин, τi = 0,5 мин). Вход и выходы реакторов 1–4, экран программы.</t>
+          <t>Таблица 1. Система 1 — 4 РИС-н последовательно (vi = 50 л/мин, τi = 0,5 мин). Экран: τ = 0 и 0,5.</t>
         </is>
       </c>
     </row>
@@ -1389,808 +1389,325 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="11" t="n">
-        <v>0.2308</v>
+        <v>0.6498</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>23.076</v>
+        <v>10.506</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.1923</v>
+        <v>0.3964</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>5.769</v>
+        <v>11.892</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.0385</v>
+        <v>0.2535</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1.155</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>0.4083</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>17.751</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0.3082</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>9.245999999999999</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0.1001</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>3.003</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>0.5448</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>13.656</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>0.3706</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>11.118</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0.1742</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>5.226</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>0.6498</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>10.506</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0.3964</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>11.892</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0.2535</v>
-      </c>
-      <c r="G11" s="6" t="n">
         <v>7.605</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Таблица 2. Система 2 — четыре РИС-н параллельно (vi = 12,5 л/мин, τi = 2 мин). Аппараты одинаковы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Таблица 2. Система 2 — 4 РИС-н параллельно. Экран: τ = 0 и 0,5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Система 2</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6" t="n">
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="11" t="n">
+      <c r="D15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B16" s="11" t="n">
         <v>0.5454</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C16" s="10" t="n">
         <v>13.638</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D16" s="11" t="n">
         <v>0.303</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E16" s="10" t="n">
         <v>9.09</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F16" s="11" t="n">
         <v>0.2424</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G16" s="10" t="n">
         <v>7.272</v>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Таблица 3. Система 3 — четыре РИВ последовательно (vi = 50 л/мин, Στ = 2 мин). Эквивалентно одному РИВ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Таблица 3. Система 3 — 4 РИВ последовательно (τi = 0,5 мин). Экран: τ = 0 и 0,5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Система 3</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6" t="n">
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B27" s="11" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>3.258</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B28" s="9" t="n">
-        <v>0.2134</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>0.1965</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B29" s="11" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>1.065</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B30" s="9" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>1.773</v>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>9.036000000000001</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>13.332</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>7.632000000000001</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Таблица 4. Система 4 — 4 РИВ параллельно. Экран: τ = 0 и 0,5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Система 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>2.601</v>
+      <c r="A31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B32" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>4.494</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B34" s="9" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>5.517</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>6.567</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B36" s="9" t="n">
+      <c r="A32" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B32" s="11" t="n">
         <v>0.6988</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C32" s="10" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D32" s="11" t="n">
         <v>0.4444</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E32" s="10" t="n">
         <v>13.332</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F32" s="11" t="n">
         <v>0.2544</v>
       </c>
-      <c r="G36" s="6" t="n">
-        <v>7.632000000000001</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Таблица 4. Система 4 — четыре РИВ параллельно (vi = 12,5 л/мин, τi = 2 мин). Выход как у единичного РИВ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>Система 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C44" s="10" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>3.258</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G44" s="10" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B45" s="9" t="n">
-        <v>0.2134</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>0.1965</v>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C46" s="10" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G46" s="10" t="n">
-        <v>1.065</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B47" s="9" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D47" s="9" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>1.773</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C48" s="10" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F48" s="11" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G48" s="10" t="n">
-        <v>2.601</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F49" s="9" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>3.516</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D50" s="11" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F50" s="11" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G50" s="10" t="n">
-        <v>4.494</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B51" s="9" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D51" s="9" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E51" s="6" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F51" s="9" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>5.517</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C52" s="10" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F52" s="11" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G52" s="10" t="n">
-        <v>6.567</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" s="9" t="n">
-        <v>0.6988</v>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>9.036000000000001</v>
-      </c>
-      <c r="D53" s="9" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="F53" s="9" t="n">
-        <v>0.2544</v>
-      </c>
-      <c r="G53" s="6" t="n">
+      <c r="G32" s="10" t="n">
         <v>7.632000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
+++ b/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1306,21 +1306,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Пункт 2. Четыре таблицы — по одной на каждую исследуемую систему</t>
+          <t>Пункт 2. Таблица с результатами моделирования для каждого реактора каждой системы (колонки как в бланке: Тау, X, CA, Y, CR, Z, CS)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Таблица 1. Система 1 — 4 РИС-н последовательно (vi = 50 л/мин, τi = 0,5 мин). Экран: τ = 0 и 0,5.</t>
+          <t>Система 1. Четыре последовательно соединённых РИС-н одинакового объёма (vi = 50 л/мин, τi = 0,5 мин). Экран программы, локальное Тау аппарата.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Система 1</t>
+          <t>Реактор 1</t>
         </is>
       </c>
     </row>
@@ -1389,326 +1389,1418 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="11" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>23.076</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>5.769</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>1.155</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>23.076</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>5.769</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.155</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>17.751</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>9.245999999999999</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>3.003</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>17.751</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>9.245999999999999</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>3.003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>13.656</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>11.118</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>5.226</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>13.656</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>11.118</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>5.226</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B26" s="11" t="n">
         <v>0.6498</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C26" s="10" t="n">
         <v>10.506</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D26" s="11" t="n">
         <v>0.3964</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E26" s="10" t="n">
         <v>11.892</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F26" s="11" t="n">
         <v>0.2535</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G26" s="10" t="n">
         <v>7.605</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Таблица 2. Система 2 — 4 РИС-н параллельно. Экран: τ = 0 и 0,5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Система 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Система 2. Четыре параллельно соединённых РИС-н, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин). Аппараты одинаковы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="n">
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>13.638</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>7.272</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>13.638</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>7.272</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>13.638</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>7.272</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>13.638</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>7.272</v>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Система 3. Четыре последовательно соединённых РИВ одинакового объёма (vi = 50 л/мин, τi = 0,5 мин).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="B16" s="11" t="n">
-        <v>0.5454</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>13.638</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>0.2424</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>7.272</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Таблица 3. Система 3 — 4 РИВ последовательно (τi = 0,5 мин). Экран: τ = 0 и 0,5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Система 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="B60" s="11" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>22.224</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>7.011</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>0.762</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6" t="n">
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>22.224</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>7.011</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>0.762</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>16.464</v>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>10.935</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>2.601</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>16.464</v>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>10.935</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>2.601</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>0.5934</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>12.198</v>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>12.801</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>5.000999999999999</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>0.5934</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>12.198</v>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>12.801</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>5.000999999999999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="C78" s="10" t="n">
+        <v>9.036000000000001</v>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>13.332</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>7.632000000000001</v>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Система 4. Четыре параллельно соединённых РИВ, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин). Аппараты одинаковы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B24" s="11" t="n">
+      <c r="D85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B86" s="11" t="n">
         <v>0.6988</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C86" s="10" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D86" s="11" t="n">
         <v>0.4444</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E86" s="10" t="n">
         <v>13.332</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F86" s="11" t="n">
         <v>0.2544</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G86" s="10" t="n">
         <v>7.632000000000001</v>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Таблица 4. Система 4 — 4 РИВ параллельно. Экран: τ = 0 и 0,5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Система 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="6" t="n">
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B32" s="11" t="n">
+      <c r="D91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B92" s="11" t="n">
         <v>0.6988</v>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C92" s="10" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D92" s="11" t="n">
         <v>0.4444</v>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="E92" s="10" t="n">
         <v>13.332</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F92" s="11" t="n">
         <v>0.2544</v>
       </c>
-      <c r="G32" s="10" t="n">
+      <c r="G92" s="10" t="n">
         <v>7.632000000000001</v>
       </c>
     </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B98" s="11" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="C98" s="10" t="n">
+        <v>9.036000000000001</v>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>13.332</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>7.632000000000001</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>Реактор 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" s="11" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="C104" s="10" t="n">
+        <v>9.036000000000001</v>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>13.332</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>7.632000000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A13:G13"/>
+  <mergeCells count="21">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A89:G89"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A101:G101"/>
+    <mergeCell ref="A57:G57"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
+++ b/reaktory_sistemy_variant2/Reaktornye_sistemy_variant2.xlsx
@@ -1680,7 +1680,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Система 2. Четыре параллельно соединённых РИС-н, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин). Аппараты одинаковы.</t>
+          <t>Система 2. Четыре параллельно соединённых РИС-н, одинаковая нагрузка. На экране τ = 0 и 0,5. Аппараты одинаковы.</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>0.5454</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B40" s="11" t="n">
         <v>0.5454</v>
@@ -1933,7 +1933,7 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B46" s="11" t="n">
         <v>0.5454</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B52" s="11" t="n">
         <v>0.5454</v>
@@ -2414,7 +2414,7 @@
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Система 4. Четыре параллельно соединённых РИВ, одинаковая нагрузка (vi = 12,5 л/мин, τi = 2 мин). Аппараты одинаковы.</t>
+          <t>Система 4. Четыре параллельно соединённых РИВ, одинаковая нагрузка. На экране τ = 0 и 0,5. Аппараты одинаковы.</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="86">
       <c r="A86" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B86" s="11" t="n">
         <v>0.6988</v>
@@ -2577,7 +2577,7 @@
     </row>
     <row r="92">
       <c r="A92" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B92" s="11" t="n">
         <v>0.6988</v>
@@ -2667,7 +2667,7 @@
     </row>
     <row r="98">
       <c r="A98" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B98" s="11" t="n">
         <v>0.6988</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="104">
       <c r="A104" s="10" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="B104" s="11" t="n">
         <v>0.6988</v>
